--- a/agentic-qe-mvp/demo-artifacts/flow-1-hotel-e2e-CYC-3/09-report/CYC-3-cycle-report.xlsx
+++ b/agentic-qe-mvp/demo-artifacts/flow-1-hotel-e2e-CYC-3/09-report/CYC-3-cycle-report.xlsx
@@ -161,7 +161,7 @@
     <t>sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform (35af1ef)</t>
   </si>
   <si>
-    <t>Pulled live from GitHub: git clone of sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform (35af1ef) at 2026-10-02T03:54:05.425Z</t>
+    <t>Pulled live from GitHub: git clone of sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform (35af1ef) at 2026-10-02T04:13:45.754Z</t>
   </si>
   <si>
     <t>ID</t>
@@ -1377,7 +1377,7 @@
     <t>Priya Shah</t>
   </si>
   <si>
-    <t>2026-10-02T03:54:06.246Z</t>
+    <t>2026-10-02T04:13:46.483Z</t>
   </si>
   <si>
     <t>128 requirements approved; 0 excluded; 0 conflict(s) resolved</t>
@@ -5548,7 +5548,7 @@
         <v>387</v>
       </c>
       <c r="E2" s="2">
-        <v>1083</v>
+        <v>1028</v>
       </c>
       <c r="F2" s="2"/>
     </row>
@@ -5566,7 +5566,7 @@
         <v>387</v>
       </c>
       <c r="E3" s="2">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="F3" s="2"/>
     </row>
@@ -5584,7 +5584,7 @@
         <v>387</v>
       </c>
       <c r="E4" s="2">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F4" s="2"/>
     </row>
@@ -5602,7 +5602,7 @@
         <v>387</v>
       </c>
       <c r="E5" s="2">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="F5" s="2"/>
     </row>
@@ -5620,7 +5620,7 @@
         <v>387</v>
       </c>
       <c r="E6" s="2">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="F6" s="2"/>
     </row>
@@ -5638,7 +5638,7 @@
         <v>387</v>
       </c>
       <c r="E7" s="2">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F7" s="2"/>
     </row>
@@ -5656,7 +5656,7 @@
         <v>387</v>
       </c>
       <c r="E8" s="2">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="F8" s="2"/>
     </row>
@@ -5674,7 +5674,7 @@
         <v>387</v>
       </c>
       <c r="E9" s="2">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F9" s="2"/>
     </row>

--- a/agentic-qe-mvp/demo-artifacts/flow-1-hotel-e2e-CYC-3/09-report/CYC-3-cycle-report.xlsx
+++ b/agentic-qe-mvp/demo-artifacts/flow-1-hotel-e2e-CYC-3/09-report/CYC-3-cycle-report.xlsx
@@ -161,7 +161,7 @@
     <t>sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform (35af1ef)</t>
   </si>
   <si>
-    <t>Pulled live from GitHub: git clone of sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform (35af1ef) at 2026-10-02T04:13:45.754Z</t>
+    <t>Pulled live from GitHub: git clone of sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform (35af1ef) at 2026-10-02T15:08:27.184Z</t>
   </si>
   <si>
     <t>ID</t>
@@ -1377,7 +1377,7 @@
     <t>Priya Shah</t>
   </si>
   <si>
-    <t>2026-10-02T04:13:46.483Z</t>
+    <t>2026-10-02T15:08:28.180Z</t>
   </si>
   <si>
     <t>128 requirements approved; 0 excluded; 0 conflict(s) resolved</t>
@@ -1518,7 +1518,7 @@
     <t>End-to-end testing from the user's point of view</t>
   </si>
   <si>
-    <t>Steers the design agents to write browser journeys as the travel advisor experiences them.</t>
+    <t>Steers the design agents to write journeys as the guest experiences them, from search to confirmation.</t>
   </si>
   <si>
     <t>testcases, scripts, execution</t>
@@ -5548,7 +5548,7 @@
         <v>387</v>
       </c>
       <c r="E2" s="2">
-        <v>1028</v>
+        <v>1115</v>
       </c>
       <c r="F2" s="2"/>
     </row>
@@ -5566,7 +5566,7 @@
         <v>387</v>
       </c>
       <c r="E3" s="2">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="F3" s="2"/>
     </row>
@@ -5584,7 +5584,7 @@
         <v>387</v>
       </c>
       <c r="E4" s="2">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="F4" s="2"/>
     </row>
@@ -5602,7 +5602,7 @@
         <v>387</v>
       </c>
       <c r="E5" s="2">
-        <v>72</v>
+        <v>97</v>
       </c>
       <c r="F5" s="2"/>
     </row>
@@ -5620,7 +5620,7 @@
         <v>387</v>
       </c>
       <c r="E6" s="2">
-        <v>64</v>
+        <v>78</v>
       </c>
       <c r="F6" s="2"/>
     </row>
@@ -5638,7 +5638,7 @@
         <v>387</v>
       </c>
       <c r="E7" s="2">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F7" s="2"/>
     </row>
@@ -5656,7 +5656,7 @@
         <v>387</v>
       </c>
       <c r="E8" s="2">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="F8" s="2"/>
     </row>
@@ -5674,7 +5674,7 @@
         <v>387</v>
       </c>
       <c r="E9" s="2">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="F9" s="2"/>
     </row>

--- a/agentic-qe-mvp/demo-artifacts/flow-1-hotel-e2e-CYC-3/09-report/CYC-3-cycle-report.xlsx
+++ b/agentic-qe-mvp/demo-artifacts/flow-1-hotel-e2e-CYC-3/09-report/CYC-3-cycle-report.xlsx
@@ -161,7 +161,7 @@
     <t>sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform (35af1ef)</t>
   </si>
   <si>
-    <t>Pulled live from GitHub: git clone of sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform (35af1ef) at 2026-10-02T15:08:27.184Z</t>
+    <t>Pulled live from GitHub: git clone of sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform (35af1ef) at 2026-10-02T15:29:42.911Z</t>
   </si>
   <si>
     <t>ID</t>
@@ -1377,7 +1377,7 @@
     <t>Priya Shah</t>
   </si>
   <si>
-    <t>2026-10-02T15:08:28.180Z</t>
+    <t>2026-10-02T15:29:43.709Z</t>
   </si>
   <si>
     <t>128 requirements approved; 0 excluded; 0 conflict(s) resolved</t>
@@ -5548,7 +5548,7 @@
         <v>387</v>
       </c>
       <c r="E2" s="2">
-        <v>1115</v>
+        <v>1142</v>
       </c>
       <c r="F2" s="2"/>
     </row>
@@ -5566,7 +5566,7 @@
         <v>387</v>
       </c>
       <c r="E3" s="2">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="F3" s="2"/>
     </row>
@@ -5584,7 +5584,7 @@
         <v>387</v>
       </c>
       <c r="E4" s="2">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F4" s="2"/>
     </row>
@@ -5602,7 +5602,7 @@
         <v>387</v>
       </c>
       <c r="E5" s="2">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="F5" s="2"/>
     </row>
@@ -5620,7 +5620,7 @@
         <v>387</v>
       </c>
       <c r="E6" s="2">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="F6" s="2"/>
     </row>
@@ -5638,7 +5638,7 @@
         <v>387</v>
       </c>
       <c r="E7" s="2">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F7" s="2"/>
     </row>
@@ -5656,7 +5656,7 @@
         <v>387</v>
       </c>
       <c r="E8" s="2">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="F8" s="2"/>
     </row>
@@ -5674,7 +5674,7 @@
         <v>387</v>
       </c>
       <c r="E9" s="2">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F9" s="2"/>
     </row>

--- a/agentic-qe-mvp/demo-artifacts/flow-1-hotel-e2e-CYC-3/09-report/CYC-3-cycle-report.xlsx
+++ b/agentic-qe-mvp/demo-artifacts/flow-1-hotel-e2e-CYC-3/09-report/CYC-3-cycle-report.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1324" uniqueCount="535">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1324" uniqueCount="537">
   <si>
     <t>Metric</t>
   </si>
@@ -113,7 +113,7 @@
     <t>Narrative</t>
   </si>
   <si>
-    <t>Hotel booking baseline · End-to-end (baseline) worked from Jira initiative AQPI-1 (pulled live from GitHub), Jira epic AQPI-2, AQPI-6, AQPI-10, AQPI-14, AQPI-18, AQPI-23, AQPI-27 (pulled live from GitHub), Codebase sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform (35af1ef) (pulled live from GitHub). The reviewed requirement set holds 128 requirements. 8 test cases are designed, 8 of them automated in 7 Playwright scripts. Execution ran 8 automated cases for real: 8 passed and 0 failed (pass rate 100%). No defects were raised.</t>
+    <t>Hotel booking baseline · End-to-end (baseline) worked from Jira initiative AQPI-1 (Jira export on GitHub), Jira epic AQPI-2, AQPI-6, AQPI-10, AQPI-14, AQPI-18, AQPI-23, AQPI-27 (Jira export on GitHub), Codebase sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform (35af1ef) (pulled live from GitHub). The reviewed requirement set holds 128 requirements. 8 test cases are designed, 8 of them automated in 7 Playwright scripts. Execution ran 8 automated cases for real: 8 passed and 0 failed (pass rate 100%). No defects were raised.</t>
   </si>
   <si>
     <t>Narrative drafted by</t>
@@ -143,25 +143,31 @@
     <t>AQPI-1</t>
   </si>
   <si>
+    <t>jira-export</t>
+  </si>
+  <si>
+    <t>Jira export on GitHub (sri465inno/uc-agentic-quality-engineering@demo/jira-export): Jira REST API v3 JSON of AQPI-1, exported from https://tcs-team-ou6drgfr.atlassian.net; no live Jira call was made</t>
+  </si>
+  <si>
+    <t>Jira epic</t>
+  </si>
+  <si>
+    <t>AQPI-2, AQPI-6, AQPI-10, AQPI-14, AQPI-18, AQPI-23, AQPI-27</t>
+  </si>
+  <si>
+    <t>Jira export on GitHub (sri465inno/uc-agentic-quality-engineering@demo/jira-export): Jira REST API v3 JSON of AQPI-2, exported from https://tcs-team-ou6drgfr.atlassian.net; no live Jira call was made</t>
+  </si>
+  <si>
+    <t>Codebase</t>
+  </si>
+  <si>
+    <t>sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform (35af1ef)</t>
+  </si>
+  <si>
     <t>github</t>
   </si>
   <si>
-    <t>Jira REST API v3 export pulled live from GitHub (sri465inno/uc-agentic-quality-engineering@demo/jira-export) - synthetic test issues; no live Jira call was made</t>
-  </si>
-  <si>
-    <t>Jira epic</t>
-  </si>
-  <si>
-    <t>AQPI-2, AQPI-6, AQPI-10, AQPI-14, AQPI-18, AQPI-23, AQPI-27</t>
-  </si>
-  <si>
-    <t>Codebase</t>
-  </si>
-  <si>
-    <t>sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform (35af1ef)</t>
-  </si>
-  <si>
-    <t>Pulled live from GitHub: git clone of sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform (35af1ef) at 2026-10-02T15:29:42.911Z</t>
+    <t>Pulled live from GitHub: git clone of sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform (35af1ef) at 2026-10-02T16:18:27.590Z</t>
   </si>
   <si>
     <t>ID</t>
@@ -1377,7 +1383,7 @@
     <t>Priya Shah</t>
   </si>
   <si>
-    <t>2026-10-02T15:29:43.709Z</t>
+    <t>2026-10-02T16:18:28.425Z</t>
   </si>
   <si>
     <t>128 requirements approved; 0 excluded; 0 conflict(s) resolved</t>
@@ -2229,189 +2235,189 @@
   <sheetData>
     <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="2" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="3" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="4" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="5" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="6" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="7" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="8" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="9" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="10" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="11" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
   </sheetData>
@@ -2434,186 +2440,186 @@
   <sheetData>
     <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="2" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="3" spans="2:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B3" s="2" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="4" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="5" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="6" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
     </row>
     <row r="7" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
     </row>
     <row r="8" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
     </row>
     <row r="9" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
     </row>
     <row r="10" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
     </row>
     <row r="11" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
     </row>
   </sheetData>
@@ -2681,24 +2687,24 @@
         <v>40</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C4" s="2">
         <v>7</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -2722,36 +2728,36 @@
   <sheetData>
     <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="2" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E2" s="2">
         <v>1</v>
@@ -2760,16 +2766,16 @@
     </row>
     <row r="3" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E3" s="2">
         <v>1</v>
@@ -2778,16 +2784,16 @@
     </row>
     <row r="4" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E4" s="2">
         <v>1</v>
@@ -2796,16 +2802,16 @@
     </row>
     <row r="5" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E5" s="2">
         <v>1</v>
@@ -2814,16 +2820,16 @@
     </row>
     <row r="6" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E6" s="2">
         <v>1</v>
@@ -2832,16 +2838,16 @@
     </row>
     <row r="7" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E7" s="2">
         <v>1</v>
@@ -2850,16 +2856,16 @@
     </row>
     <row r="8" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E8" s="2">
         <v>1</v>
@@ -2868,16 +2874,16 @@
     </row>
     <row r="9" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E9" s="2">
         <v>1</v>
@@ -2886,16 +2892,16 @@
     </row>
     <row r="10" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E10" s="2">
         <v>1</v>
@@ -2904,16 +2910,16 @@
     </row>
     <row r="11" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E11" s="2">
         <v>1</v>
@@ -2922,16 +2928,16 @@
     </row>
     <row r="12" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E12" s="2">
         <v>1</v>
@@ -2940,16 +2946,16 @@
     </row>
     <row r="13" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E13" s="2">
         <v>1</v>
@@ -2958,16 +2964,16 @@
     </row>
     <row r="14" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E14" s="2">
         <v>1</v>
@@ -2976,16 +2982,16 @@
     </row>
     <row r="15" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E15" s="2">
         <v>1</v>
@@ -2994,16 +3000,16 @@
     </row>
     <row r="16" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E16" s="2">
         <v>1</v>
@@ -3012,16 +3018,16 @@
     </row>
     <row r="17" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E17" s="2">
         <v>1</v>
@@ -3030,16 +3036,16 @@
     </row>
     <row r="18" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E18" s="2">
         <v>1</v>
@@ -3048,16 +3054,16 @@
     </row>
     <row r="19" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E19" s="2">
         <v>1</v>
@@ -3066,16 +3072,16 @@
     </row>
     <row r="20" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E20" s="2">
         <v>1</v>
@@ -3084,16 +3090,16 @@
     </row>
     <row r="21" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E21" s="2">
         <v>1</v>
@@ -3102,16 +3108,16 @@
     </row>
     <row r="22" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E22" s="2">
         <v>1</v>
@@ -3120,16 +3126,16 @@
     </row>
     <row r="23" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E23" s="2">
         <v>1</v>
@@ -3138,16 +3144,16 @@
     </row>
     <row r="24" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E24" s="2">
         <v>1</v>
@@ -3156,16 +3162,16 @@
     </row>
     <row r="25" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E25" s="2">
         <v>1</v>
@@ -3174,16 +3180,16 @@
     </row>
     <row r="26" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E26" s="2">
         <v>1</v>
@@ -3192,16 +3198,16 @@
     </row>
     <row r="27" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E27" s="2">
         <v>1</v>
@@ -3210,16 +3216,16 @@
     </row>
     <row r="28" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E28" s="2">
         <v>1</v>
@@ -3228,16 +3234,16 @@
     </row>
     <row r="29" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E29" s="2">
         <v>1</v>
@@ -3246,16 +3252,16 @@
     </row>
     <row r="30" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E30" s="2">
         <v>1</v>
@@ -3264,16 +3270,16 @@
     </row>
     <row r="31" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E31" s="2">
         <v>1</v>
@@ -3282,16 +3288,16 @@
     </row>
     <row r="32" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E32" s="2">
         <v>1</v>
@@ -3300,16 +3306,16 @@
     </row>
     <row r="33" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E33" s="2">
         <v>1</v>
@@ -3318,16 +3324,16 @@
     </row>
     <row r="34" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E34" s="2">
         <v>1</v>
@@ -3336,16 +3342,16 @@
     </row>
     <row r="35" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E35" s="2">
         <v>1</v>
@@ -3354,16 +3360,16 @@
     </row>
     <row r="36" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E36" s="2">
         <v>1</v>
@@ -3372,16 +3378,16 @@
     </row>
     <row r="37" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E37" s="2">
         <v>1</v>
@@ -3390,16 +3396,16 @@
     </row>
     <row r="38" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E38" s="2">
         <v>1</v>
@@ -3408,16 +3414,16 @@
     </row>
     <row r="39" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E39" s="2">
         <v>1</v>
@@ -3426,16 +3432,16 @@
     </row>
     <row r="40" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E40" s="2">
         <v>1</v>
@@ -3444,16 +3450,16 @@
     </row>
     <row r="41" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E41" s="2">
         <v>1</v>
@@ -3462,16 +3468,16 @@
     </row>
     <row r="42" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E42" s="2">
         <v>1</v>
@@ -3480,16 +3486,16 @@
     </row>
     <row r="43" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E43" s="2">
         <v>1</v>
@@ -3498,16 +3504,16 @@
     </row>
     <row r="44" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E44" s="2">
         <v>1</v>
@@ -3516,16 +3522,16 @@
     </row>
     <row r="45" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E45" s="2">
         <v>1</v>
@@ -3534,16 +3540,16 @@
     </row>
     <row r="46" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E46" s="2">
         <v>1</v>
@@ -3552,16 +3558,16 @@
     </row>
     <row r="47" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E47" s="2">
         <v>1</v>
@@ -3570,16 +3576,16 @@
     </row>
     <row r="48" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E48" s="2">
         <v>1</v>
@@ -3588,16 +3594,16 @@
     </row>
     <row r="49" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E49" s="2">
         <v>1</v>
@@ -3606,16 +3612,16 @@
     </row>
     <row r="50" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E50" s="2">
         <v>1</v>
@@ -3624,16 +3630,16 @@
     </row>
     <row r="51" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E51" s="2">
         <v>1</v>
@@ -3642,16 +3648,16 @@
     </row>
     <row r="52" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E52" s="2">
         <v>1</v>
@@ -3660,16 +3666,16 @@
     </row>
     <row r="53" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E53" s="2">
         <v>1</v>
@@ -3678,16 +3684,16 @@
     </row>
     <row r="54" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E54" s="2">
         <v>1</v>
@@ -3696,16 +3702,16 @@
     </row>
     <row r="55" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E55" s="2">
         <v>1</v>
@@ -3714,16 +3720,16 @@
     </row>
     <row r="56" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E56" s="2">
         <v>1</v>
@@ -3732,16 +3738,16 @@
     </row>
     <row r="57" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E57" s="2">
         <v>1</v>
@@ -3750,16 +3756,16 @@
     </row>
     <row r="58" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E58" s="2">
         <v>1</v>
@@ -3768,16 +3774,16 @@
     </row>
     <row r="59" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E59" s="2">
         <v>1</v>
@@ -3786,16 +3792,16 @@
     </row>
     <row r="60" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E60" s="2">
         <v>1</v>
@@ -3804,16 +3810,16 @@
     </row>
     <row r="61" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E61" s="2">
         <v>1</v>
@@ -3822,16 +3828,16 @@
     </row>
     <row r="62" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E62" s="2">
         <v>1</v>
@@ -3840,16 +3846,16 @@
     </row>
     <row r="63" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E63" s="2">
         <v>1</v>
@@ -3858,16 +3864,16 @@
     </row>
     <row r="64" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E64" s="2">
         <v>1</v>
@@ -3876,16 +3882,16 @@
     </row>
     <row r="65" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E65" s="2">
         <v>1</v>
@@ -3894,16 +3900,16 @@
     </row>
     <row r="66" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E66" s="2">
         <v>1</v>
@@ -3912,16 +3918,16 @@
     </row>
     <row r="67" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E67" s="2">
         <v>1</v>
@@ -3930,16 +3936,16 @@
     </row>
     <row r="68" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E68" s="2">
         <v>1</v>
@@ -3948,16 +3954,16 @@
     </row>
     <row r="69" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E69" s="2">
         <v>1</v>
@@ -3966,16 +3972,16 @@
     </row>
     <row r="70" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E70" s="2">
         <v>1</v>
@@ -3984,16 +3990,16 @@
     </row>
     <row r="71" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E71" s="2">
         <v>1</v>
@@ -4002,16 +4008,16 @@
     </row>
     <row r="72" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E72" s="2">
         <v>1</v>
@@ -4020,16 +4026,16 @@
     </row>
     <row r="73" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E73" s="2">
         <v>1</v>
@@ -4038,16 +4044,16 @@
     </row>
     <row r="74" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E74" s="2">
         <v>1</v>
@@ -4056,16 +4062,16 @@
     </row>
     <row r="75" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E75" s="2">
         <v>1</v>
@@ -4074,16 +4080,16 @@
     </row>
     <row r="76" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E76" s="2">
         <v>1</v>
@@ -4092,16 +4098,16 @@
     </row>
     <row r="77" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E77" s="2">
         <v>1</v>
@@ -4110,16 +4116,16 @@
     </row>
     <row r="78" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E78" s="2">
         <v>1</v>
@@ -4128,16 +4134,16 @@
     </row>
     <row r="79" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E79" s="2">
         <v>1</v>
@@ -4146,16 +4152,16 @@
     </row>
     <row r="80" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E80" s="2">
         <v>1</v>
@@ -4164,16 +4170,16 @@
     </row>
     <row r="81" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E81" s="2">
         <v>1</v>
@@ -4182,16 +4188,16 @@
     </row>
     <row r="82" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E82" s="2">
         <v>1</v>
@@ -4200,16 +4206,16 @@
     </row>
     <row r="83" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E83" s="2">
         <v>1</v>
@@ -4218,16 +4224,16 @@
     </row>
     <row r="84" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E84" s="2">
         <v>1</v>
@@ -4236,16 +4242,16 @@
     </row>
     <row r="85" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E85" s="2">
         <v>1</v>
@@ -4254,16 +4260,16 @@
     </row>
     <row r="86" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E86" s="2">
         <v>1</v>
@@ -4272,16 +4278,16 @@
     </row>
     <row r="87" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E87" s="2">
         <v>1</v>
@@ -4290,16 +4296,16 @@
     </row>
     <row r="88" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E88" s="2">
         <v>1</v>
@@ -4308,16 +4314,16 @@
     </row>
     <row r="89" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E89" s="2">
         <v>1</v>
@@ -4326,16 +4332,16 @@
     </row>
     <row r="90" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E90" s="2">
         <v>1</v>
@@ -4344,16 +4350,16 @@
     </row>
     <row r="91" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E91" s="2">
         <v>1</v>
@@ -4362,16 +4368,16 @@
     </row>
     <row r="92" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E92" s="2">
         <v>1</v>
@@ -4380,16 +4386,16 @@
     </row>
     <row r="93" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E93" s="2">
         <v>1</v>
@@ -4398,16 +4404,16 @@
     </row>
     <row r="94" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E94" s="2">
         <v>1</v>
@@ -4416,16 +4422,16 @@
     </row>
     <row r="95" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E95" s="2">
         <v>1</v>
@@ -4434,16 +4440,16 @@
     </row>
     <row r="96" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E96" s="2">
         <v>1</v>
@@ -4452,16 +4458,16 @@
     </row>
     <row r="97" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E97" s="2">
         <v>1</v>
@@ -4470,16 +4476,16 @@
     </row>
     <row r="98" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E98" s="2">
         <v>1</v>
@@ -4488,16 +4494,16 @@
     </row>
     <row r="99" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E99" s="2">
         <v>1</v>
@@ -4506,16 +4512,16 @@
     </row>
     <row r="100" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E100" s="2">
         <v>1</v>
@@ -4524,16 +4530,16 @@
     </row>
     <row r="101" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E101" s="2">
         <v>1</v>
@@ -4542,16 +4548,16 @@
     </row>
     <row r="102" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E102" s="2">
         <v>1</v>
@@ -4560,16 +4566,16 @@
     </row>
     <row r="103" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E103" s="2">
         <v>1</v>
@@ -4578,16 +4584,16 @@
     </row>
     <row r="104" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E104" s="2">
         <v>1</v>
@@ -4596,16 +4602,16 @@
     </row>
     <row r="105" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E105" s="2">
         <v>1</v>
@@ -4614,16 +4620,16 @@
     </row>
     <row r="106" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E106" s="2">
         <v>1</v>
@@ -4632,16 +4638,16 @@
     </row>
     <row r="107" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E107" s="2">
         <v>1</v>
@@ -4650,16 +4656,16 @@
     </row>
     <row r="108" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E108" s="2">
         <v>1</v>
@@ -4668,16 +4674,16 @@
     </row>
     <row r="109" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E109" s="2">
         <v>1</v>
@@ -4686,16 +4692,16 @@
     </row>
     <row r="110" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E110" s="2">
         <v>1</v>
@@ -4704,16 +4710,16 @@
     </row>
     <row r="111" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E111" s="2">
         <v>1</v>
@@ -4722,16 +4728,16 @@
     </row>
     <row r="112" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E112" s="2">
         <v>1</v>
@@ -4740,16 +4746,16 @@
     </row>
     <row r="113" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E113" s="2">
         <v>1</v>
@@ -4758,16 +4764,16 @@
     </row>
     <row r="114" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E114" s="2">
         <v>1</v>
@@ -4776,16 +4782,16 @@
     </row>
     <row r="115" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E115" s="2">
         <v>1</v>
@@ -4794,16 +4800,16 @@
     </row>
     <row r="116" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E116" s="2">
         <v>1</v>
@@ -4812,16 +4818,16 @@
     </row>
     <row r="117" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E117" s="2">
         <v>1</v>
@@ -4830,16 +4836,16 @@
     </row>
     <row r="118" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E118" s="2">
         <v>1</v>
@@ -4848,16 +4854,16 @@
     </row>
     <row r="119" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E119" s="2">
         <v>1</v>
@@ -4866,16 +4872,16 @@
     </row>
     <row r="120" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E120" s="2">
         <v>1</v>
@@ -4884,16 +4890,16 @@
     </row>
     <row r="121" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E121" s="2">
         <v>1</v>
@@ -4902,16 +4908,16 @@
     </row>
     <row r="122" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E122" s="2">
         <v>1</v>
@@ -4920,16 +4926,16 @@
     </row>
     <row r="123" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E123" s="2">
         <v>1</v>
@@ -4938,16 +4944,16 @@
     </row>
     <row r="124" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E124" s="2">
         <v>1</v>
@@ -4956,16 +4962,16 @@
     </row>
     <row r="125" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E125" s="2">
         <v>1</v>
@@ -4974,16 +4980,16 @@
     </row>
     <row r="126" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E126" s="2">
         <v>1</v>
@@ -4992,16 +4998,16 @@
     </row>
     <row r="127" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E127" s="2">
         <v>1</v>
@@ -5010,16 +5016,16 @@
     </row>
     <row r="128" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E128" s="2">
         <v>1</v>
@@ -5028,16 +5034,16 @@
     </row>
     <row r="129" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A129" s="2" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E129" s="2">
         <v>1</v>
@@ -5073,425 +5079,425 @@
   <sheetData>
     <row r="1" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="M1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="2" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="N2" s="2" t="s">
         <v>8</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="3" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="M3" s="2" t="s">
         <v>338</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>340</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>341</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>342</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>343</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>333</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>334</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>335</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>336</v>
       </c>
       <c r="N3" s="2" t="s">
         <v>8</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="4" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="N4" s="2" t="s">
         <v>8</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="5" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="N5" s="2" t="s">
         <v>8</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="6" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="N6" s="2" t="s">
         <v>8</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="7" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="N7" s="2" t="s">
         <v>8</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="8" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="N8" s="2" t="s">
         <v>8</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="9" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="N9" s="2" t="s">
         <v>8</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
   </sheetData>
@@ -5516,144 +5522,144 @@
   <sheetData>
     <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="2" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="E2" s="2">
-        <v>1142</v>
+        <v>1187</v>
       </c>
       <c r="F2" s="2"/>
     </row>
     <row r="3" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="E3" s="2">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="F3" s="2"/>
     </row>
     <row r="4" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="E4" s="2">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="F4" s="2"/>
     </row>
     <row r="5" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="E5" s="2">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="F5" s="2"/>
     </row>
     <row r="6" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="E6" s="2">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="F6" s="2"/>
     </row>
     <row r="7" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="E7" s="2">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F7" s="2"/>
     </row>
     <row r="8" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="E8" s="2">
         <v>57</v>
@@ -5662,19 +5668,19 @@
     </row>
     <row r="9" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="E9" s="2">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="F9" s="2"/>
     </row>
@@ -5699,31 +5705,31 @@
   <sheetData>
     <row r="1" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
   </sheetData>
@@ -5747,19 +5753,19 @@
   <sheetData>
     <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>23</v>
@@ -5770,10 +5776,10 @@
     </row>
     <row r="2" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C2" s="2">
         <v>2</v>
@@ -5788,15 +5794,15 @@
         <v>0</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="3" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C3" s="2">
         <v>1</v>
@@ -5811,15 +5817,15 @@
         <v>0</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="4" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C4" s="2">
         <v>0</v>
@@ -5834,15 +5840,15 @@
         <v>0</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="5" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C5" s="2">
         <v>1</v>
@@ -5857,15 +5863,15 @@
         <v>0</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="6" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C6" s="2">
         <v>1</v>
@@ -5880,15 +5886,15 @@
         <v>0</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="7" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C7" s="2">
         <v>1</v>
@@ -5903,15 +5909,15 @@
         <v>0</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="8" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C8" s="2">
         <v>1</v>
@@ -5926,15 +5932,15 @@
         <v>0</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="9" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C9" s="2">
         <v>0</v>
@@ -5949,15 +5955,15 @@
         <v>0</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="10" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C10" s="2">
         <v>0</v>
@@ -5972,15 +5978,15 @@
         <v>0</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="11" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C11" s="2">
         <v>0</v>
@@ -5995,15 +6001,15 @@
         <v>0</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="12" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C12" s="2">
         <v>0</v>
@@ -6018,15 +6024,15 @@
         <v>0</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="13" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C13" s="2">
         <v>0</v>
@@ -6041,15 +6047,15 @@
         <v>0</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="14" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C14" s="2">
         <v>0</v>
@@ -6064,15 +6070,15 @@
         <v>0</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="15" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C15" s="2">
         <v>0</v>
@@ -6087,15 +6093,15 @@
         <v>0</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="16" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C16" s="2">
         <v>0</v>
@@ -6110,15 +6116,15 @@
         <v>0</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="17" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C17" s="2">
         <v>0</v>
@@ -6133,15 +6139,15 @@
         <v>0</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="18" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C18" s="2">
         <v>0</v>
@@ -6156,15 +6162,15 @@
         <v>0</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="19" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C19" s="2">
         <v>0</v>
@@ -6179,15 +6185,15 @@
         <v>0</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="20" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C20" s="2">
         <v>0</v>
@@ -6202,15 +6208,15 @@
         <v>0</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="21" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C21" s="2">
         <v>0</v>
@@ -6225,15 +6231,15 @@
         <v>0</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="22" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C22" s="2">
         <v>0</v>
@@ -6248,15 +6254,15 @@
         <v>0</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="23" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C23" s="2">
         <v>0</v>
@@ -6271,15 +6277,15 @@
         <v>0</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="24" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C24" s="2">
         <v>0</v>
@@ -6294,15 +6300,15 @@
         <v>0</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="25" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C25" s="2">
         <v>0</v>
@@ -6317,15 +6323,15 @@
         <v>0</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="26" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C26" s="2">
         <v>0</v>
@@ -6340,15 +6346,15 @@
         <v>0</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="27" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C27" s="2">
         <v>0</v>
@@ -6363,15 +6369,15 @@
         <v>0</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="28" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C28" s="2">
         <v>0</v>
@@ -6386,15 +6392,15 @@
         <v>0</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="29" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C29" s="2">
         <v>0</v>
@@ -6409,15 +6415,15 @@
         <v>0</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="30" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C30" s="2">
         <v>0</v>
@@ -6432,15 +6438,15 @@
         <v>0</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="31" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C31" s="2">
         <v>0</v>
@@ -6455,15 +6461,15 @@
         <v>0</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="32" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C32" s="2">
         <v>0</v>
@@ -6478,15 +6484,15 @@
         <v>0</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="33" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C33" s="2">
         <v>0</v>
@@ -6501,15 +6507,15 @@
         <v>0</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="34" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C34" s="2">
         <v>0</v>
@@ -6524,15 +6530,15 @@
         <v>0</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="35" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C35" s="2">
         <v>0</v>
@@ -6547,15 +6553,15 @@
         <v>0</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="36" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C36" s="2">
         <v>0</v>
@@ -6570,15 +6576,15 @@
         <v>0</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="37" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C37" s="2">
         <v>0</v>
@@ -6593,15 +6599,15 @@
         <v>0</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="38" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C38" s="2">
         <v>0</v>
@@ -6616,15 +6622,15 @@
         <v>0</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="39" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C39" s="2">
         <v>0</v>
@@ -6639,15 +6645,15 @@
         <v>0</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="40" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C40" s="2">
         <v>0</v>
@@ -6662,15 +6668,15 @@
         <v>0</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="41" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C41" s="2">
         <v>0</v>
@@ -6685,15 +6691,15 @@
         <v>0</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="42" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C42" s="2">
         <v>0</v>
@@ -6708,15 +6714,15 @@
         <v>0</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="43" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C43" s="2">
         <v>0</v>
@@ -6731,15 +6737,15 @@
         <v>0</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="44" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C44" s="2">
         <v>0</v>
@@ -6754,15 +6760,15 @@
         <v>0</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="45" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C45" s="2">
         <v>0</v>
@@ -6777,15 +6783,15 @@
         <v>0</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="46" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C46" s="2">
         <v>0</v>
@@ -6800,15 +6806,15 @@
         <v>0</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="47" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C47" s="2">
         <v>0</v>
@@ -6823,15 +6829,15 @@
         <v>0</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="48" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C48" s="2">
         <v>0</v>
@@ -6846,15 +6852,15 @@
         <v>0</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="49" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C49" s="2">
         <v>0</v>
@@ -6869,15 +6875,15 @@
         <v>0</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="50" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C50" s="2">
         <v>0</v>
@@ -6892,15 +6898,15 @@
         <v>0</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="51" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C51" s="2">
         <v>0</v>
@@ -6915,15 +6921,15 @@
         <v>0</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="52" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C52" s="2">
         <v>1</v>
@@ -6938,15 +6944,15 @@
         <v>0</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="53" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C53" s="2">
         <v>0</v>
@@ -6961,15 +6967,15 @@
         <v>0</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="54" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C54" s="2">
         <v>0</v>
@@ -6984,15 +6990,15 @@
         <v>0</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="55" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C55" s="2">
         <v>0</v>
@@ -7007,15 +7013,15 @@
         <v>0</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="56" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C56" s="2">
         <v>0</v>
@@ -7030,15 +7036,15 @@
         <v>0</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="57" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C57" s="2">
         <v>0</v>
@@ -7053,15 +7059,15 @@
         <v>0</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="58" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C58" s="2">
         <v>0</v>
@@ -7076,15 +7082,15 @@
         <v>0</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="59" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C59" s="2">
         <v>0</v>
@@ -7099,15 +7105,15 @@
         <v>0</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="60" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C60" s="2">
         <v>0</v>
@@ -7122,15 +7128,15 @@
         <v>0</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="61" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C61" s="2">
         <v>0</v>
@@ -7145,15 +7151,15 @@
         <v>0</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="62" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C62" s="2">
         <v>0</v>
@@ -7168,15 +7174,15 @@
         <v>0</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="63" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C63" s="2">
         <v>0</v>
@@ -7191,15 +7197,15 @@
         <v>0</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="64" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C64" s="2">
         <v>0</v>
@@ -7214,15 +7220,15 @@
         <v>0</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="65" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C65" s="2">
         <v>0</v>
@@ -7237,15 +7243,15 @@
         <v>0</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="66" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C66" s="2">
         <v>0</v>
@@ -7260,15 +7266,15 @@
         <v>0</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="67" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C67" s="2">
         <v>0</v>
@@ -7283,15 +7289,15 @@
         <v>0</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="68" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="C68" s="2">
         <v>0</v>
@@ -7306,15 +7312,15 @@
         <v>0</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="69" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C69" s="2">
         <v>0</v>
@@ -7329,15 +7335,15 @@
         <v>0</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="70" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C70" s="2">
         <v>0</v>
@@ -7352,15 +7358,15 @@
         <v>0</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="71" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C71" s="2">
         <v>0</v>
@@ -7375,15 +7381,15 @@
         <v>0</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="72" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="C72" s="2">
         <v>0</v>
@@ -7398,15 +7404,15 @@
         <v>0</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="73" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="C73" s="2">
         <v>0</v>
@@ -7421,15 +7427,15 @@
         <v>0</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="74" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C74" s="2">
         <v>0</v>
@@ -7444,15 +7450,15 @@
         <v>0</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="75" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C75" s="2">
         <v>0</v>
@@ -7467,15 +7473,15 @@
         <v>0</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="76" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C76" s="2">
         <v>0</v>
@@ -7490,15 +7496,15 @@
         <v>0</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="77" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C77" s="2">
         <v>0</v>
@@ -7513,15 +7519,15 @@
         <v>0</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="78" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="C78" s="2">
         <v>0</v>
@@ -7536,15 +7542,15 @@
         <v>0</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="79" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C79" s="2">
         <v>0</v>
@@ -7559,15 +7565,15 @@
         <v>0</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="80" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C80" s="2">
         <v>0</v>
@@ -7582,15 +7588,15 @@
         <v>0</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="81" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C81" s="2">
         <v>0</v>
@@ -7605,15 +7611,15 @@
         <v>0</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="82" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C82" s="2">
         <v>0</v>
@@ -7628,15 +7634,15 @@
         <v>0</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="83" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C83" s="2">
         <v>0</v>
@@ -7651,15 +7657,15 @@
         <v>0</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="84" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C84" s="2">
         <v>0</v>
@@ -7674,15 +7680,15 @@
         <v>0</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="85" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C85" s="2">
         <v>0</v>
@@ -7697,15 +7703,15 @@
         <v>0</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="86" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="C86" s="2">
         <v>0</v>
@@ -7720,15 +7726,15 @@
         <v>0</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="87" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C87" s="2">
         <v>0</v>
@@ -7743,15 +7749,15 @@
         <v>0</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="88" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C88" s="2">
         <v>0</v>
@@ -7766,15 +7772,15 @@
         <v>0</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="89" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="C89" s="2">
         <v>0</v>
@@ -7789,15 +7795,15 @@
         <v>0</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="90" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C90" s="2">
         <v>0</v>
@@ -7812,15 +7818,15 @@
         <v>0</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="91" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C91" s="2">
         <v>0</v>
@@ -7835,15 +7841,15 @@
         <v>0</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="92" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C92" s="2">
         <v>0</v>
@@ -7858,15 +7864,15 @@
         <v>0</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="93" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C93" s="2">
         <v>0</v>
@@ -7881,15 +7887,15 @@
         <v>0</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="94" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C94" s="2">
         <v>0</v>
@@ -7904,15 +7910,15 @@
         <v>0</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="95" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C95" s="2">
         <v>0</v>
@@ -7927,15 +7933,15 @@
         <v>0</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="96" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C96" s="2">
         <v>0</v>
@@ -7950,15 +7956,15 @@
         <v>0</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="97" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="C97" s="2">
         <v>0</v>
@@ -7973,15 +7979,15 @@
         <v>0</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="98" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="C98" s="2">
         <v>0</v>
@@ -7996,15 +8002,15 @@
         <v>0</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="99" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C99" s="2">
         <v>0</v>
@@ -8019,15 +8025,15 @@
         <v>0</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="100" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C100" s="2">
         <v>0</v>
@@ -8042,15 +8048,15 @@
         <v>0</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="101" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C101" s="2">
         <v>0</v>
@@ -8065,15 +8071,15 @@
         <v>0</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="102" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C102" s="2">
         <v>0</v>
@@ -8088,15 +8094,15 @@
         <v>0</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="103" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="C103" s="2">
         <v>0</v>
@@ -8111,15 +8117,15 @@
         <v>0</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="104" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="C104" s="2">
         <v>0</v>
@@ -8134,15 +8140,15 @@
         <v>0</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="105" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="C105" s="2">
         <v>0</v>
@@ -8157,15 +8163,15 @@
         <v>0</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="106" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="C106" s="2">
         <v>0</v>
@@ -8180,15 +8186,15 @@
         <v>0</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="107" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="C107" s="2">
         <v>0</v>
@@ -8203,15 +8209,15 @@
         <v>0</v>
       </c>
       <c r="G107" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="108" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="C108" s="2">
         <v>0</v>
@@ -8226,15 +8232,15 @@
         <v>0</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="109" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="C109" s="2">
         <v>0</v>
@@ -8249,15 +8255,15 @@
         <v>0</v>
       </c>
       <c r="G109" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="110" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="C110" s="2">
         <v>0</v>
@@ -8272,15 +8278,15 @@
         <v>0</v>
       </c>
       <c r="G110" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="111" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="C111" s="2">
         <v>0</v>
@@ -8295,15 +8301,15 @@
         <v>0</v>
       </c>
       <c r="G111" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="112" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C112" s="2">
         <v>0</v>
@@ -8318,15 +8324,15 @@
         <v>0</v>
       </c>
       <c r="G112" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="113" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="C113" s="2">
         <v>0</v>
@@ -8341,15 +8347,15 @@
         <v>0</v>
       </c>
       <c r="G113" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="114" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C114" s="2">
         <v>0</v>
@@ -8364,15 +8370,15 @@
         <v>0</v>
       </c>
       <c r="G114" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="115" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C115" s="2">
         <v>0</v>
@@ -8387,15 +8393,15 @@
         <v>0</v>
       </c>
       <c r="G115" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="116" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="C116" s="2">
         <v>0</v>
@@ -8410,15 +8416,15 @@
         <v>0</v>
       </c>
       <c r="G116" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="117" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="C117" s="2">
         <v>0</v>
@@ -8433,15 +8439,15 @@
         <v>0</v>
       </c>
       <c r="G117" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="118" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="C118" s="2">
         <v>0</v>
@@ -8456,15 +8462,15 @@
         <v>0</v>
       </c>
       <c r="G118" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="119" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C119" s="2">
         <v>0</v>
@@ -8479,15 +8485,15 @@
         <v>0</v>
       </c>
       <c r="G119" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="120" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="C120" s="2">
         <v>0</v>
@@ -8502,15 +8508,15 @@
         <v>0</v>
       </c>
       <c r="G120" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="121" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="C121" s="2">
         <v>0</v>
@@ -8525,15 +8531,15 @@
         <v>0</v>
       </c>
       <c r="G121" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="122" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="C122" s="2">
         <v>0</v>
@@ -8548,15 +8554,15 @@
         <v>0</v>
       </c>
       <c r="G122" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="123" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="C123" s="2">
         <v>0</v>
@@ -8571,15 +8577,15 @@
         <v>0</v>
       </c>
       <c r="G123" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="124" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C124" s="2">
         <v>0</v>
@@ -8594,15 +8600,15 @@
         <v>0</v>
       </c>
       <c r="G124" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="125" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="C125" s="2">
         <v>0</v>
@@ -8617,15 +8623,15 @@
         <v>0</v>
       </c>
       <c r="G125" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="126" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="C126" s="2">
         <v>0</v>
@@ -8640,15 +8646,15 @@
         <v>0</v>
       </c>
       <c r="G126" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="127" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="C127" s="2">
         <v>0</v>
@@ -8663,15 +8669,15 @@
         <v>0</v>
       </c>
       <c r="G127" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="128" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="C128" s="2">
         <v>0</v>
@@ -8686,15 +8692,15 @@
         <v>0</v>
       </c>
       <c r="G128" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="129" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A129" s="2" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="C129" s="2">
         <v>0</v>
@@ -8709,7 +8715,7 @@
         <v>0</v>
       </c>
       <c r="G129" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
   </sheetData>
@@ -8731,13 +8737,13 @@
   <sheetData>
     <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>6</v>
@@ -8745,212 +8751,212 @@
     </row>
     <row r="2" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="3" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="4" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>410</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>337</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>408</v>
       </c>
     </row>
     <row r="5" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="6" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="7" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="8" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="9" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="10" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="11" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="12" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="13" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="14" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="15" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="16" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
   </sheetData>
@@ -8973,36 +8979,36 @@
   <sheetData>
     <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="2" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
   </sheetData>

--- a/agentic-qe-mvp/demo-artifacts/flow-1-hotel-e2e-CYC-3/09-report/CYC-3-cycle-report.xlsx
+++ b/agentic-qe-mvp/demo-artifacts/flow-1-hotel-e2e-CYC-3/09-report/CYC-3-cycle-report.xlsx
@@ -12,16 +12,18 @@
     <sheet sheetId="6" name="Defects" state="visible" r:id="rId9"/>
     <sheet sheetId="7" name="Coverage" state="visible" r:id="rId10"/>
     <sheet sheetId="8" name="Attribute coverage" state="visible" r:id="rId11"/>
-    <sheet sheetId="9" name="Approvals" state="visible" r:id="rId12"/>
-    <sheet sheetId="10" name="Skills" state="visible" r:id="rId13"/>
-    <sheet sheetId="11" name="Hand-overs" state="visible" r:id="rId14"/>
+    <sheet sheetId="9" name="Traceability by story" state="visible" r:id="rId12"/>
+    <sheet sheetId="10" name="Traceability matrix" state="visible" r:id="rId13"/>
+    <sheet sheetId="11" name="Approvals" state="visible" r:id="rId14"/>
+    <sheet sheetId="12" name="Skills" state="visible" r:id="rId15"/>
+    <sheet sheetId="13" name="Hand-overs" state="visible" r:id="rId16"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1324" uniqueCount="537">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1640" uniqueCount="638">
   <si>
     <t>Metric</t>
   </si>
@@ -167,7 +169,7 @@
     <t>github</t>
   </si>
   <si>
-    <t>Pulled live from GitHub: git clone of sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform (35af1ef) at 2026-10-02T16:18:27.590Z</t>
+    <t>Pulled live from GitHub: git clone of sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform (35af1ef) at 2026-10-02T19:27:46.786Z</t>
   </si>
   <si>
     <t>ID</t>
@@ -1218,6 +1220,12 @@
     <t>Severity</t>
   </si>
   <si>
+    <t>Story</t>
+  </si>
+  <si>
+    <t>Jira defect</t>
+  </si>
+  <si>
     <t>Expected</t>
   </si>
   <si>
@@ -1359,6 +1367,303 @@
     <t>Prefix of the Idempotency-Key sent with a reservation (the full key is 8 to 64 characters)</t>
   </si>
   <si>
+    <t>Jira item</t>
+  </si>
+  <si>
+    <t>Level</t>
+  </si>
+  <si>
+    <t>Parent</t>
+  </si>
+  <si>
+    <t>Summary</t>
+  </si>
+  <si>
+    <t>initiative</t>
+  </si>
+  <si>
+    <t>[Initiative] Intelligent Hotel Shopping and Reservation Experience</t>
+  </si>
+  <si>
+    <t>verified</t>
+  </si>
+  <si>
+    <t>AQPI-2</t>
+  </si>
+  <si>
+    <t>epic</t>
+  </si>
+  <si>
+    <t>[Epic 1] Search and Availability</t>
+  </si>
+  <si>
+    <t>AQPI-3</t>
+  </si>
+  <si>
+    <t>story</t>
+  </si>
+  <si>
+    <t>3.1 Search hotels by destination and date range</t>
+  </si>
+  <si>
+    <t>AQPI-4</t>
+  </si>
+  <si>
+    <t>3.2 Validate occupancy and stay criteria</t>
+  </si>
+  <si>
+    <t>AQPI-5</t>
+  </si>
+  <si>
+    <t>3.3 Handle unavailable or failed searches</t>
+  </si>
+  <si>
+    <t>AQPI-6</t>
+  </si>
+  <si>
+    <t>[Epic 2] Hotel Results and Selection</t>
+  </si>
+  <si>
+    <t>AQPI-7</t>
+  </si>
+  <si>
+    <t>4.1 Display available hotels</t>
+  </si>
+  <si>
+    <t>AQPI-8</t>
+  </si>
+  <si>
+    <t>4.2 Sort and filter hotel results</t>
+  </si>
+  <si>
+    <t>AQPI-9</t>
+  </si>
+  <si>
+    <t>4.3 View hotel and room details</t>
+  </si>
+  <si>
+    <t>AQPI-10</t>
+  </si>
+  <si>
+    <t>[Epic 3] Personalized Ancillary Offers</t>
+  </si>
+  <si>
+    <t>AQPI-11</t>
+  </si>
+  <si>
+    <t>5.1 Determine eligible ancillary offers</t>
+  </si>
+  <si>
+    <t>AQPI-12</t>
+  </si>
+  <si>
+    <t>5.2 Display ancillary offers</t>
+  </si>
+  <si>
+    <t>AQPI-13</t>
+  </si>
+  <si>
+    <t>5.3 Explain and control personalization</t>
+  </si>
+  <si>
+    <t>AQPI-14</t>
+  </si>
+  <si>
+    <t>[Epic 4] Cart Management</t>
+  </si>
+  <si>
+    <t>AQPI-15</t>
+  </si>
+  <si>
+    <t>6.1 Add room selection to cart</t>
+  </si>
+  <si>
+    <t>AQPI-16</t>
+  </si>
+  <si>
+    <t>6.2 Add, update, and remove ancillaries</t>
+  </si>
+  <si>
+    <t>AQPI-17</t>
+  </si>
+  <si>
+    <t>6.3 Review cart and total price</t>
+  </si>
+  <si>
+    <t>AQPI-18</t>
+  </si>
+  <si>
+    <t>[Epic 5] Checkout and Reservation</t>
+  </si>
+  <si>
+    <t>AQPI-19</t>
+  </si>
+  <si>
+    <t>7.1 Capture guest and contact information</t>
+  </si>
+  <si>
+    <t>AQPI-20</t>
+  </si>
+  <si>
+    <t>7.2 Capture and authorize payment</t>
+  </si>
+  <si>
+    <t>AQPI-21</t>
+  </si>
+  <si>
+    <t>7.3 Create reservation idempotently</t>
+  </si>
+  <si>
+    <t>AQPI-22</t>
+  </si>
+  <si>
+    <t>7.4 Show booking outcome</t>
+  </si>
+  <si>
+    <t>AQPI-23</t>
+  </si>
+  <si>
+    <t>[Epic 6] Confirmation and Notifications</t>
+  </si>
+  <si>
+    <t>AQPI-24</t>
+  </si>
+  <si>
+    <t>8.1 Generate confirmation message</t>
+  </si>
+  <si>
+    <t>AQPI-25</t>
+  </si>
+  <si>
+    <t>8.2 Send and track confirmation email</t>
+  </si>
+  <si>
+    <t>AQPI-26</t>
+  </si>
+  <si>
+    <t>8.3 Resend confirmation safely</t>
+  </si>
+  <si>
+    <t>AQPI-27</t>
+  </si>
+  <si>
+    <t>[Epic 7] Cross-Cutting Quality, Privacy and Observability</t>
+  </si>
+  <si>
+    <t>AQPI-28</t>
+  </si>
+  <si>
+    <t>9.1 Protect sensitive data</t>
+  </si>
+  <si>
+    <t>AQPI-29</t>
+  </si>
+  <si>
+    <t>9.2 Provide end-to-end observability</t>
+  </si>
+  <si>
+    <t>AQPI-30</t>
+  </si>
+  <si>
+    <t>9.3 Meet accessibility requirements</t>
+  </si>
+  <si>
+    <t>AQPI-31</t>
+  </si>
+  <si>
+    <t>9.4 Meet performance and reliability objectives</t>
+  </si>
+  <si>
+    <t>Jira</t>
+  </si>
+  <si>
+    <t>Requirement text</t>
+  </si>
+  <si>
+    <t>Rule</t>
+  </si>
+  <si>
+    <t>Test case</t>
+  </si>
+  <si>
+    <t>Automation</t>
+  </si>
+  <si>
+    <t>Test data</t>
+  </si>
+  <si>
+    <t>Script</t>
+  </si>
+  <si>
+    <t>Defect</t>
+  </si>
+  <si>
+    <t>BR-001</t>
+  </si>
+  <si>
+    <t>TD-F-001</t>
+  </si>
+  <si>
+    <t>br-001-booking-journey.spec.js</t>
+  </si>
+  <si>
+    <t>TD-F-002</t>
+  </si>
+  <si>
+    <t>BR-002</t>
+  </si>
+  <si>
+    <t>TD-F-003</t>
+  </si>
+  <si>
+    <t>br-002-bookable-inventory.spec.js</t>
+  </si>
+  <si>
+    <t>BR-004</t>
+  </si>
+  <si>
+    <t>TD-F-004</t>
+  </si>
+  <si>
+    <t>br-004-offers-not-blocking.spec.js</t>
+  </si>
+  <si>
+    <t>BR-005</t>
+  </si>
+  <si>
+    <t>TD-F-005</t>
+  </si>
+  <si>
+    <t>br-005-duplicate-submission.spec.js</t>
+  </si>
+  <si>
+    <t>BR-006</t>
+  </si>
+  <si>
+    <t>TD-F-006</t>
+  </si>
+  <si>
+    <t>br-006-durable-confirmation.spec.js</t>
+  </si>
+  <si>
+    <t>BR-007</t>
+  </si>
+  <si>
+    <t>TD-F-007</t>
+  </si>
+  <si>
+    <t>br-007-confirmation-shown.spec.js</t>
+  </si>
+  <si>
+    <t>BR-051</t>
+  </si>
+  <si>
+    <t>TD-F-008</t>
+  </si>
+  <si>
+    <t>br-051-offers-not-blocking.spec.js</t>
+  </si>
+  <si>
     <t>Gate</t>
   </si>
   <si>
@@ -1383,7 +1688,7 @@
     <t>Priya Shah</t>
   </si>
   <si>
-    <t>2026-10-02T16:18:28.425Z</t>
+    <t>2026-10-02T19:27:47.566Z</t>
   </si>
   <si>
     <t>128 requirements approved; 0 excluded; 0 conflict(s) resolved</t>
@@ -2223,6 +2528,451 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:M9"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="16" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="3" max="3" width="60" customWidth="1"/>
+    <col min="5" max="5" width="11" customWidth="1"/>
+    <col min="6" max="6" width="50" customWidth="1"/>
+    <col min="7" max="7" width="12" customWidth="1"/>
+    <col min="8" max="9" width="11" customWidth="1"/>
+    <col min="10" max="10" width="40" customWidth="1"/>
+    <col min="11" max="11" width="14" customWidth="1"/>
+    <col min="12" max="12" width="10" customWidth="1"/>
+    <col min="13" max="13" width="12" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>510</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>513</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>514</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>515</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>518</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>519</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>520</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>518</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>520</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>522</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>524</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="M4" s="2" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>525</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>526</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="M5" s="2" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>528</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>530</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="M6" s="2" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>531</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>533</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="L7" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="M7" s="2" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>535</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>536</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="M8" s="2" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>537</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>538</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>539</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="M9" s="2" t="s">
+        <v>339</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="26" customWidth="1"/>
+    <col min="2" max="2" width="10" customWidth="1"/>
+    <col min="3" max="3" width="18" customWidth="1"/>
+    <col min="4" max="4" width="26" customWidth="1"/>
+    <col min="5" max="5" width="80" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>540</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>541</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>542</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>546</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>547</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>548</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>549</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
@@ -2235,189 +2985,189 @@
   <sheetData>
     <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>449</v>
+        <v>550</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>314</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>450</v>
+        <v>551</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>451</v>
+        <v>552</v>
       </c>
     </row>
     <row r="2" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>452</v>
+        <v>553</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>453</v>
+        <v>554</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>454</v>
+        <v>555</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>455</v>
+        <v>556</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>456</v>
+        <v>557</v>
       </c>
     </row>
     <row r="3" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>457</v>
+        <v>558</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>458</v>
+        <v>559</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>459</v>
+        <v>560</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>460</v>
+        <v>561</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>461</v>
+        <v>562</v>
       </c>
     </row>
     <row r="4" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>462</v>
+        <v>563</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>463</v>
+        <v>564</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>464</v>
+        <v>565</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>465</v>
+        <v>566</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>466</v>
+        <v>567</v>
       </c>
     </row>
     <row r="5" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>467</v>
+        <v>568</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>468</v>
+        <v>569</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>469</v>
+        <v>570</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>470</v>
+        <v>571</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>471</v>
+        <v>572</v>
       </c>
     </row>
     <row r="6" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>472</v>
+        <v>573</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>473</v>
+        <v>574</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>474</v>
+        <v>575</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>475</v>
+        <v>576</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>476</v>
+        <v>577</v>
       </c>
     </row>
     <row r="7" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>477</v>
+        <v>578</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>478</v>
+        <v>579</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>479</v>
+        <v>580</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>480</v>
+        <v>581</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>481</v>
+        <v>582</v>
       </c>
     </row>
     <row r="8" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>482</v>
+        <v>583</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>483</v>
+        <v>584</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>484</v>
+        <v>585</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>485</v>
+        <v>586</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>486</v>
+        <v>587</v>
       </c>
     </row>
     <row r="9" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>487</v>
+        <v>588</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>488</v>
+        <v>589</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>489</v>
+        <v>590</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>490</v>
+        <v>591</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>491</v>
+        <v>592</v>
       </c>
     </row>
     <row r="10" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>492</v>
+        <v>593</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>493</v>
+        <v>594</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>494</v>
+        <v>595</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>495</v>
+        <v>596</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>496</v>
+        <v>597</v>
       </c>
     </row>
     <row r="11" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>497</v>
+        <v>598</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>498</v>
+        <v>599</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>499</v>
+        <v>600</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>500</v>
+        <v>601</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>501</v>
+        <v>602</v>
       </c>
     </row>
   </sheetData>
@@ -2426,7 +3176,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
@@ -2440,186 +3190,186 @@
   <sheetData>
     <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>502</v>
+        <v>603</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>503</v>
+        <v>604</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>504</v>
+        <v>605</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>505</v>
+        <v>606</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>506</v>
+        <v>607</v>
       </c>
     </row>
     <row r="2" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>507</v>
+        <v>608</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>508</v>
+        <v>609</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>509</v>
+        <v>610</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>339</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>510</v>
+        <v>611</v>
       </c>
     </row>
     <row r="3" spans="2:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B3" s="2" t="s">
-        <v>477</v>
+        <v>578</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>509</v>
+        <v>610</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>339</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>511</v>
+        <v>612</v>
       </c>
     </row>
     <row r="4" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>512</v>
+        <v>613</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>497</v>
+        <v>598</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>509</v>
+        <v>610</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>339</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>513</v>
+        <v>614</v>
       </c>
     </row>
     <row r="5" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>514</v>
+        <v>615</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>515</v>
+        <v>616</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>509</v>
+        <v>610</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>339</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>516</v>
+        <v>617</v>
       </c>
     </row>
     <row r="6" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>517</v>
+        <v>618</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>518</v>
+        <v>619</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>509</v>
+        <v>610</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>339</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>519</v>
+        <v>620</v>
       </c>
     </row>
     <row r="7" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>520</v>
+        <v>621</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>521</v>
+        <v>622</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>509</v>
+        <v>610</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>339</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>522</v>
+        <v>623</v>
       </c>
     </row>
     <row r="8" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>523</v>
+        <v>624</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>524</v>
+        <v>625</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>509</v>
+        <v>610</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>339</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>525</v>
+        <v>626</v>
       </c>
     </row>
     <row r="9" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>526</v>
+        <v>627</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>527</v>
+        <v>628</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>528</v>
+        <v>629</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>529</v>
+        <v>630</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>530</v>
+        <v>631</v>
       </c>
     </row>
     <row r="10" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>531</v>
+        <v>632</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>532</v>
+        <v>633</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>509</v>
+        <v>610</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>339</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>533</v>
+        <v>634</v>
       </c>
     </row>
     <row r="11" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>534</v>
+        <v>635</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>535</v>
+        <v>636</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>509</v>
+        <v>610</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>339</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>536</v>
+        <v>637</v>
       </c>
     </row>
   </sheetData>
@@ -5554,7 +6304,7 @@
         <v>389</v>
       </c>
       <c r="E2" s="2">
-        <v>1187</v>
+        <v>1182</v>
       </c>
       <c r="F2" s="2"/>
     </row>
@@ -5572,7 +6322,7 @@
         <v>389</v>
       </c>
       <c r="E3" s="2">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="F3" s="2"/>
     </row>
@@ -5590,7 +6340,7 @@
         <v>389</v>
       </c>
       <c r="E4" s="2">
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="F4" s="2"/>
     </row>
@@ -5608,7 +6358,7 @@
         <v>389</v>
       </c>
       <c r="E5" s="2">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="F5" s="2"/>
     </row>
@@ -5626,7 +6376,7 @@
         <v>389</v>
       </c>
       <c r="E6" s="2">
-        <v>72</v>
+        <v>58</v>
       </c>
       <c r="F6" s="2"/>
     </row>
@@ -5644,7 +6394,7 @@
         <v>389</v>
       </c>
       <c r="E7" s="2">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="F7" s="2"/>
     </row>
@@ -5662,7 +6412,7 @@
         <v>389</v>
       </c>
       <c r="E8" s="2">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F8" s="2"/>
     </row>
@@ -5692,18 +6442,20 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:K1"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="2" max="2" width="50" customWidth="1"/>
-    <col min="4" max="4" width="10" customWidth="1"/>
-    <col min="5" max="5" width="12" customWidth="1"/>
-    <col min="6" max="7" width="14" customWidth="1"/>
-    <col min="8" max="8" width="50" customWidth="1"/>
-    <col min="9" max="9" width="12" customWidth="1"/>
+    <col min="4" max="4" width="11" customWidth="1"/>
+    <col min="5" max="5" width="40" customWidth="1"/>
+    <col min="6" max="6" width="10" customWidth="1"/>
+    <col min="7" max="7" width="12" customWidth="1"/>
+    <col min="8" max="9" width="14" customWidth="1"/>
+    <col min="10" max="10" width="50" customWidth="1"/>
+    <col min="11" max="11" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>49</v>
       </c>
@@ -5714,22 +6466,28 @@
         <v>391</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>385</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>50</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>392</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>393</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>394</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>395</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>397</v>
       </c>
     </row>
   </sheetData>
@@ -5756,16 +6514,16 @@
         <v>50</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>337</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>23</v>
@@ -5794,7 +6552,7 @@
         <v>0</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="3" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -5817,7 +6575,7 @@
         <v>0</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="4" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -5840,7 +6598,7 @@
         <v>0</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="5" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -5863,7 +6621,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="6" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -5886,7 +6644,7 @@
         <v>0</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="7" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -5909,7 +6667,7 @@
         <v>0</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="8" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -5932,7 +6690,7 @@
         <v>0</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="9" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -5955,7 +6713,7 @@
         <v>0</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="10" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -5978,7 +6736,7 @@
         <v>0</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="11" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6001,7 +6759,7 @@
         <v>0</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="12" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6024,7 +6782,7 @@
         <v>0</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="13" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6047,7 +6805,7 @@
         <v>0</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="14" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6070,7 +6828,7 @@
         <v>0</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="15" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6093,7 +6851,7 @@
         <v>0</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="16" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6116,7 +6874,7 @@
         <v>0</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="17" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6139,7 +6897,7 @@
         <v>0</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="18" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6162,7 +6920,7 @@
         <v>0</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="19" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6185,7 +6943,7 @@
         <v>0</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="20" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6208,7 +6966,7 @@
         <v>0</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="21" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6231,7 +6989,7 @@
         <v>0</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="22" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6254,7 +7012,7 @@
         <v>0</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="23" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6277,7 +7035,7 @@
         <v>0</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="24" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6300,7 +7058,7 @@
         <v>0</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="25" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6323,7 +7081,7 @@
         <v>0</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="26" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6346,7 +7104,7 @@
         <v>0</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="27" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6369,7 +7127,7 @@
         <v>0</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="28" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6392,7 +7150,7 @@
         <v>0</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="29" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6415,7 +7173,7 @@
         <v>0</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="30" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6438,7 +7196,7 @@
         <v>0</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="31" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6461,7 +7219,7 @@
         <v>0</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="32" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6484,7 +7242,7 @@
         <v>0</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="33" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6507,7 +7265,7 @@
         <v>0</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="34" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6530,7 +7288,7 @@
         <v>0</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="35" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6553,7 +7311,7 @@
         <v>0</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="36" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6576,7 +7334,7 @@
         <v>0</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="37" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6599,7 +7357,7 @@
         <v>0</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="38" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6622,7 +7380,7 @@
         <v>0</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="39" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6645,7 +7403,7 @@
         <v>0</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="40" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6668,7 +7426,7 @@
         <v>0</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="41" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6691,7 +7449,7 @@
         <v>0</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="42" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6714,7 +7472,7 @@
         <v>0</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="43" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6737,7 +7495,7 @@
         <v>0</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="44" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6760,7 +7518,7 @@
         <v>0</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="45" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6783,7 +7541,7 @@
         <v>0</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="46" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6806,7 +7564,7 @@
         <v>0</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="47" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6829,7 +7587,7 @@
         <v>0</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="48" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6852,7 +7610,7 @@
         <v>0</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="49" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6875,7 +7633,7 @@
         <v>0</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="50" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6898,7 +7656,7 @@
         <v>0</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="51" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6921,7 +7679,7 @@
         <v>0</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="52" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6944,7 +7702,7 @@
         <v>0</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="53" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6967,7 +7725,7 @@
         <v>0</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="54" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6990,7 +7748,7 @@
         <v>0</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="55" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7013,7 +7771,7 @@
         <v>0</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="56" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7036,7 +7794,7 @@
         <v>0</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="57" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7059,7 +7817,7 @@
         <v>0</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="58" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7082,7 +7840,7 @@
         <v>0</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="59" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7105,7 +7863,7 @@
         <v>0</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="60" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7128,7 +7886,7 @@
         <v>0</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="61" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7151,7 +7909,7 @@
         <v>0</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="62" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7174,7 +7932,7 @@
         <v>0</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="63" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7197,7 +7955,7 @@
         <v>0</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="64" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7220,7 +7978,7 @@
         <v>0</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="65" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7243,7 +8001,7 @@
         <v>0</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="66" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7266,7 +8024,7 @@
         <v>0</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="67" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7289,7 +8047,7 @@
         <v>0</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="68" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7312,7 +8070,7 @@
         <v>0</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="69" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7335,7 +8093,7 @@
         <v>0</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="70" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7358,7 +8116,7 @@
         <v>0</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="71" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7381,7 +8139,7 @@
         <v>0</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="72" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7404,7 +8162,7 @@
         <v>0</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="73" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7427,7 +8185,7 @@
         <v>0</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="74" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7450,7 +8208,7 @@
         <v>0</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="75" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7473,7 +8231,7 @@
         <v>0</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="76" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7496,7 +8254,7 @@
         <v>0</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="77" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7519,7 +8277,7 @@
         <v>0</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="78" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7542,7 +8300,7 @@
         <v>0</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="79" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7565,7 +8323,7 @@
         <v>0</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="80" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7588,7 +8346,7 @@
         <v>0</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="81" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7611,7 +8369,7 @@
         <v>0</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="82" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7634,7 +8392,7 @@
         <v>0</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="83" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7657,7 +8415,7 @@
         <v>0</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="84" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7680,7 +8438,7 @@
         <v>0</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="85" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7703,7 +8461,7 @@
         <v>0</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="86" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7726,7 +8484,7 @@
         <v>0</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="87" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7749,7 +8507,7 @@
         <v>0</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="88" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7772,7 +8530,7 @@
         <v>0</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="89" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7795,7 +8553,7 @@
         <v>0</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="90" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7818,7 +8576,7 @@
         <v>0</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="91" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7841,7 +8599,7 @@
         <v>0</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="92" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7864,7 +8622,7 @@
         <v>0</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="93" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7887,7 +8645,7 @@
         <v>0</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="94" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7910,7 +8668,7 @@
         <v>0</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="95" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7933,7 +8691,7 @@
         <v>0</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="96" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7956,7 +8714,7 @@
         <v>0</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="97" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7979,7 +8737,7 @@
         <v>0</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="98" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8002,7 +8760,7 @@
         <v>0</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="99" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8025,7 +8783,7 @@
         <v>0</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="100" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8048,7 +8806,7 @@
         <v>0</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="101" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8071,7 +8829,7 @@
         <v>0</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="102" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8094,7 +8852,7 @@
         <v>0</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="103" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8117,7 +8875,7 @@
         <v>0</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="104" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8140,7 +8898,7 @@
         <v>0</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="105" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8163,7 +8921,7 @@
         <v>0</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="106" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8186,7 +8944,7 @@
         <v>0</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="107" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8209,7 +8967,7 @@
         <v>0</v>
       </c>
       <c r="G107" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="108" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8232,7 +8990,7 @@
         <v>0</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="109" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8255,7 +9013,7 @@
         <v>0</v>
       </c>
       <c r="G109" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="110" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8278,7 +9036,7 @@
         <v>0</v>
       </c>
       <c r="G110" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="111" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8301,7 +9059,7 @@
         <v>0</v>
       </c>
       <c r="G111" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="112" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8324,7 +9082,7 @@
         <v>0</v>
       </c>
       <c r="G112" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="113" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8347,7 +9105,7 @@
         <v>0</v>
       </c>
       <c r="G113" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="114" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8370,7 +9128,7 @@
         <v>0</v>
       </c>
       <c r="G114" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="115" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8393,7 +9151,7 @@
         <v>0</v>
       </c>
       <c r="G115" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="116" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8416,7 +9174,7 @@
         <v>0</v>
       </c>
       <c r="G116" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="117" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8439,7 +9197,7 @@
         <v>0</v>
       </c>
       <c r="G117" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="118" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8462,7 +9220,7 @@
         <v>0</v>
       </c>
       <c r="G118" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="119" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8485,7 +9243,7 @@
         <v>0</v>
       </c>
       <c r="G119" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="120" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8508,7 +9266,7 @@
         <v>0</v>
       </c>
       <c r="G120" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="121" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8531,7 +9289,7 @@
         <v>0</v>
       </c>
       <c r="G121" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="122" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8554,7 +9312,7 @@
         <v>0</v>
       </c>
       <c r="G122" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="123" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8577,7 +9335,7 @@
         <v>0</v>
       </c>
       <c r="G123" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="124" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8600,7 +9358,7 @@
         <v>0</v>
       </c>
       <c r="G124" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="125" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8623,7 +9381,7 @@
         <v>0</v>
       </c>
       <c r="G125" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="126" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8646,7 +9404,7 @@
         <v>0</v>
       </c>
       <c r="G126" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="127" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8669,7 +9427,7 @@
         <v>0</v>
       </c>
       <c r="G127" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="128" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8692,7 +9450,7 @@
         <v>0</v>
       </c>
       <c r="G128" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="129" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8715,7 +9473,7 @@
         <v>0</v>
       </c>
       <c r="G129" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
   </sheetData>
@@ -8737,13 +9495,13 @@
   <sheetData>
     <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>6</v>
@@ -8751,212 +9509,212 @@
     </row>
     <row r="2" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="3" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>339</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="4" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>339</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="5" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>339</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="6" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>339</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="7" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>339</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="8" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="9" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>340</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="10" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="11" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="12" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>339</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="13" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>339</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="14" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>339</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="15" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>339</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="16" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>362</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
   </sheetData>
@@ -8967,48 +9725,1136 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:K32"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="26" customWidth="1"/>
-    <col min="2" max="2" width="10" customWidth="1"/>
-    <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="26" customWidth="1"/>
-    <col min="5" max="5" width="80" customWidth="1"/>
+    <col min="1" max="3" width="11" customWidth="1"/>
+    <col min="4" max="4" width="50" customWidth="1"/>
+    <col min="5" max="5" width="12" customWidth="1"/>
+    <col min="6" max="7" width="10" customWidth="1"/>
+    <col min="8" max="9" width="8" customWidth="1"/>
+    <col min="10" max="10" width="16" customWidth="1"/>
+    <col min="11" max="11" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>444</v>
+        <v>39</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>445</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>446</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="2">
+        <v>6</v>
+      </c>
+      <c r="F2" s="2">
+        <v>7</v>
+      </c>
+      <c r="G2" s="2">
+        <v>7</v>
+      </c>
+      <c r="H2" s="2">
+        <v>7</v>
+      </c>
+      <c r="I2" s="2">
+        <v>0</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="K2" s="2" t="s">
         <v>447</v>
       </c>
-      <c r="E2" s="2" t="s">
+    </row>
+    <row r="3" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
         <v>448</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="E3" s="2">
+        <v>0</v>
+      </c>
+      <c r="F3" s="2">
+        <v>0</v>
+      </c>
+      <c r="G3" s="2">
+        <v>0</v>
+      </c>
+      <c r="H3" s="2">
+        <v>0</v>
+      </c>
+      <c r="I3" s="2">
+        <v>0</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="E4" s="2">
+        <v>0</v>
+      </c>
+      <c r="F4" s="2">
+        <v>0</v>
+      </c>
+      <c r="G4" s="2">
+        <v>0</v>
+      </c>
+      <c r="H4" s="2">
+        <v>0</v>
+      </c>
+      <c r="I4" s="2">
+        <v>0</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="E5" s="2">
+        <v>0</v>
+      </c>
+      <c r="F5" s="2">
+        <v>0</v>
+      </c>
+      <c r="G5" s="2">
+        <v>0</v>
+      </c>
+      <c r="H5" s="2">
+        <v>0</v>
+      </c>
+      <c r="I5" s="2">
+        <v>0</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="E6" s="2">
+        <v>0</v>
+      </c>
+      <c r="F6" s="2">
+        <v>0</v>
+      </c>
+      <c r="G6" s="2">
+        <v>0</v>
+      </c>
+      <c r="H6" s="2">
+        <v>0</v>
+      </c>
+      <c r="I6" s="2">
+        <v>0</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="E7" s="2">
+        <v>0</v>
+      </c>
+      <c r="F7" s="2">
+        <v>0</v>
+      </c>
+      <c r="G7" s="2">
+        <v>0</v>
+      </c>
+      <c r="H7" s="2">
+        <v>0</v>
+      </c>
+      <c r="I7" s="2">
+        <v>0</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="E8" s="2">
+        <v>0</v>
+      </c>
+      <c r="F8" s="2">
+        <v>0</v>
+      </c>
+      <c r="G8" s="2">
+        <v>0</v>
+      </c>
+      <c r="H8" s="2">
+        <v>0</v>
+      </c>
+      <c r="I8" s="2">
+        <v>0</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="E9" s="2">
+        <v>0</v>
+      </c>
+      <c r="F9" s="2">
+        <v>0</v>
+      </c>
+      <c r="G9" s="2">
+        <v>0</v>
+      </c>
+      <c r="H9" s="2">
+        <v>0</v>
+      </c>
+      <c r="I9" s="2">
+        <v>0</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>465</v>
+      </c>
+      <c r="E10" s="2">
+        <v>0</v>
+      </c>
+      <c r="F10" s="2">
+        <v>0</v>
+      </c>
+      <c r="G10" s="2">
+        <v>0</v>
+      </c>
+      <c r="H10" s="2">
+        <v>0</v>
+      </c>
+      <c r="I10" s="2">
+        <v>0</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="E11" s="2">
+        <v>0</v>
+      </c>
+      <c r="F11" s="2">
+        <v>0</v>
+      </c>
+      <c r="G11" s="2">
+        <v>0</v>
+      </c>
+      <c r="H11" s="2">
+        <v>0</v>
+      </c>
+      <c r="I11" s="2">
+        <v>0</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>468</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="E12" s="2">
+        <v>0</v>
+      </c>
+      <c r="F12" s="2">
+        <v>0</v>
+      </c>
+      <c r="G12" s="2">
+        <v>0</v>
+      </c>
+      <c r="H12" s="2">
+        <v>0</v>
+      </c>
+      <c r="I12" s="2">
+        <v>0</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="E13" s="2">
+        <v>1</v>
+      </c>
+      <c r="F13" s="2">
+        <v>1</v>
+      </c>
+      <c r="G13" s="2">
+        <v>1</v>
+      </c>
+      <c r="H13" s="2">
+        <v>1</v>
+      </c>
+      <c r="I13" s="2">
+        <v>0</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="E14" s="2">
+        <v>0</v>
+      </c>
+      <c r="F14" s="2">
+        <v>0</v>
+      </c>
+      <c r="G14" s="2">
+        <v>0</v>
+      </c>
+      <c r="H14" s="2">
+        <v>0</v>
+      </c>
+      <c r="I14" s="2">
+        <v>0</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>475</v>
+      </c>
+      <c r="E15" s="2">
+        <v>0</v>
+      </c>
+      <c r="F15" s="2">
+        <v>0</v>
+      </c>
+      <c r="G15" s="2">
+        <v>0</v>
+      </c>
+      <c r="H15" s="2">
+        <v>0</v>
+      </c>
+      <c r="I15" s="2">
+        <v>0</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="E16" s="2">
+        <v>0</v>
+      </c>
+      <c r="F16" s="2">
+        <v>0</v>
+      </c>
+      <c r="G16" s="2">
+        <v>0</v>
+      </c>
+      <c r="H16" s="2">
+        <v>0</v>
+      </c>
+      <c r="I16" s="2">
+        <v>0</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="K16" s="2" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="E17" s="2">
+        <v>0</v>
+      </c>
+      <c r="F17" s="2">
+        <v>0</v>
+      </c>
+      <c r="G17" s="2">
+        <v>0</v>
+      </c>
+      <c r="H17" s="2">
+        <v>0</v>
+      </c>
+      <c r="I17" s="2">
+        <v>0</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="K17" s="2" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>480</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="E18" s="2">
+        <v>0</v>
+      </c>
+      <c r="F18" s="2">
+        <v>0</v>
+      </c>
+      <c r="G18" s="2">
+        <v>0</v>
+      </c>
+      <c r="H18" s="2">
+        <v>0</v>
+      </c>
+      <c r="I18" s="2">
+        <v>0</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="K18" s="2" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="E19" s="2">
+        <v>0</v>
+      </c>
+      <c r="F19" s="2">
+        <v>0</v>
+      </c>
+      <c r="G19" s="2">
+        <v>0</v>
+      </c>
+      <c r="H19" s="2">
+        <v>0</v>
+      </c>
+      <c r="I19" s="2">
+        <v>0</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="K19" s="2" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>484</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>485</v>
+      </c>
+      <c r="E20" s="2">
+        <v>0</v>
+      </c>
+      <c r="F20" s="2">
+        <v>0</v>
+      </c>
+      <c r="G20" s="2">
+        <v>0</v>
+      </c>
+      <c r="H20" s="2">
+        <v>0</v>
+      </c>
+      <c r="I20" s="2">
+        <v>0</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="K20" s="2" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="E21" s="2">
+        <v>0</v>
+      </c>
+      <c r="F21" s="2">
+        <v>0</v>
+      </c>
+      <c r="G21" s="2">
+        <v>0</v>
+      </c>
+      <c r="H21" s="2">
+        <v>0</v>
+      </c>
+      <c r="I21" s="2">
+        <v>0</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="K21" s="2" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>489</v>
+      </c>
+      <c r="E22" s="2">
+        <v>0</v>
+      </c>
+      <c r="F22" s="2">
+        <v>0</v>
+      </c>
+      <c r="G22" s="2">
+        <v>0</v>
+      </c>
+      <c r="H22" s="2">
+        <v>0</v>
+      </c>
+      <c r="I22" s="2">
+        <v>0</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="K22" s="2" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="E23" s="2">
+        <v>0</v>
+      </c>
+      <c r="F23" s="2">
+        <v>0</v>
+      </c>
+      <c r="G23" s="2">
+        <v>0</v>
+      </c>
+      <c r="H23" s="2">
+        <v>0</v>
+      </c>
+      <c r="I23" s="2">
+        <v>0</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="K23" s="2" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="E24" s="2">
+        <v>0</v>
+      </c>
+      <c r="F24" s="2">
+        <v>0</v>
+      </c>
+      <c r="G24" s="2">
+        <v>0</v>
+      </c>
+      <c r="H24" s="2">
+        <v>0</v>
+      </c>
+      <c r="I24" s="2">
+        <v>0</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="K24" s="2" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="E25" s="2">
+        <v>0</v>
+      </c>
+      <c r="F25" s="2">
+        <v>0</v>
+      </c>
+      <c r="G25" s="2">
+        <v>0</v>
+      </c>
+      <c r="H25" s="2">
+        <v>0</v>
+      </c>
+      <c r="I25" s="2">
+        <v>0</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="K25" s="2" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="E26" s="2">
+        <v>0</v>
+      </c>
+      <c r="F26" s="2">
+        <v>0</v>
+      </c>
+      <c r="G26" s="2">
+        <v>0</v>
+      </c>
+      <c r="H26" s="2">
+        <v>0</v>
+      </c>
+      <c r="I26" s="2">
+        <v>0</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="K26" s="2" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="E27" s="2">
+        <v>0</v>
+      </c>
+      <c r="F27" s="2">
+        <v>0</v>
+      </c>
+      <c r="G27" s="2">
+        <v>0</v>
+      </c>
+      <c r="H27" s="2">
+        <v>0</v>
+      </c>
+      <c r="I27" s="2">
+        <v>0</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="K27" s="2" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
+        <v>500</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>501</v>
+      </c>
+      <c r="E28" s="2">
+        <v>0</v>
+      </c>
+      <c r="F28" s="2">
+        <v>0</v>
+      </c>
+      <c r="G28" s="2">
+        <v>0</v>
+      </c>
+      <c r="H28" s="2">
+        <v>0</v>
+      </c>
+      <c r="I28" s="2">
+        <v>0</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="K28" s="2" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>500</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="E29" s="2">
+        <v>0</v>
+      </c>
+      <c r="F29" s="2">
+        <v>0</v>
+      </c>
+      <c r="G29" s="2">
+        <v>0</v>
+      </c>
+      <c r="H29" s="2">
+        <v>0</v>
+      </c>
+      <c r="I29" s="2">
+        <v>0</v>
+      </c>
+      <c r="J29" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="K29" s="2" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
+        <v>504</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>500</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>505</v>
+      </c>
+      <c r="E30" s="2">
+        <v>0</v>
+      </c>
+      <c r="F30" s="2">
+        <v>0</v>
+      </c>
+      <c r="G30" s="2">
+        <v>0</v>
+      </c>
+      <c r="H30" s="2">
+        <v>0</v>
+      </c>
+      <c r="I30" s="2">
+        <v>0</v>
+      </c>
+      <c r="J30" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="K30" s="2" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>500</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="E31" s="2">
+        <v>0</v>
+      </c>
+      <c r="F31" s="2">
+        <v>0</v>
+      </c>
+      <c r="G31" s="2">
+        <v>0</v>
+      </c>
+      <c r="H31" s="2">
+        <v>0</v>
+      </c>
+      <c r="I31" s="2">
+        <v>0</v>
+      </c>
+      <c r="J31" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="K31" s="2" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>500</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>509</v>
+      </c>
+      <c r="E32" s="2">
+        <v>0</v>
+      </c>
+      <c r="F32" s="2">
+        <v>0</v>
+      </c>
+      <c r="G32" s="2">
+        <v>0</v>
+      </c>
+      <c r="H32" s="2">
+        <v>0</v>
+      </c>
+      <c r="I32" s="2">
+        <v>0</v>
+      </c>
+      <c r="J32" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="K32" s="2" t="s">
+        <v>402</v>
       </c>
     </row>
   </sheetData>

--- a/agentic-qe-mvp/demo-artifacts/flow-1-hotel-e2e-CYC-3/09-report/CYC-3-cycle-report.xlsx
+++ b/agentic-qe-mvp/demo-artifacts/flow-1-hotel-e2e-CYC-3/09-report/CYC-3-cycle-report.xlsx
@@ -169,7 +169,7 @@
     <t>github</t>
   </si>
   <si>
-    <t>Pulled live from GitHub: git clone of sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform (35af1ef) at 2026-10-02T19:27:46.786Z</t>
+    <t>Pulled live from GitHub: git clone of sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform (35af1ef) at 2026-10-02T19:44:01.743Z</t>
   </si>
   <si>
     <t>ID</t>
@@ -1688,7 +1688,7 @@
     <t>Priya Shah</t>
   </si>
   <si>
-    <t>2026-10-02T19:27:47.566Z</t>
+    <t>2026-10-02T19:44:02.617Z</t>
   </si>
   <si>
     <t>128 requirements approved; 0 excluded; 0 conflict(s) resolved</t>
@@ -6304,7 +6304,7 @@
         <v>389</v>
       </c>
       <c r="E2" s="2">
-        <v>1182</v>
+        <v>1160</v>
       </c>
       <c r="F2" s="2"/>
     </row>
@@ -6322,7 +6322,7 @@
         <v>389</v>
       </c>
       <c r="E3" s="2">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="F3" s="2"/>
     </row>
@@ -6340,7 +6340,7 @@
         <v>389</v>
       </c>
       <c r="E4" s="2">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="F4" s="2"/>
     </row>
@@ -6358,7 +6358,7 @@
         <v>389</v>
       </c>
       <c r="E5" s="2">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="F5" s="2"/>
     </row>
@@ -6376,7 +6376,7 @@
         <v>389</v>
       </c>
       <c r="E6" s="2">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="F6" s="2"/>
     </row>
@@ -6394,7 +6394,7 @@
         <v>389</v>
       </c>
       <c r="E7" s="2">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F7" s="2"/>
     </row>
@@ -6412,7 +6412,7 @@
         <v>389</v>
       </c>
       <c r="E8" s="2">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="F8" s="2"/>
     </row>
@@ -6430,7 +6430,7 @@
         <v>389</v>
       </c>
       <c r="E9" s="2">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="F9" s="2"/>
     </row>

--- a/agentic-qe-mvp/demo-artifacts/flow-1-hotel-e2e-CYC-3/09-report/CYC-3-cycle-report.xlsx
+++ b/agentic-qe-mvp/demo-artifacts/flow-1-hotel-e2e-CYC-3/09-report/CYC-3-cycle-report.xlsx
@@ -10,20 +10,21 @@
     <sheet sheetId="4" name="Test Cases" state="visible" r:id="rId7"/>
     <sheet sheetId="5" name="Execution" state="visible" r:id="rId8"/>
     <sheet sheetId="6" name="Defects" state="visible" r:id="rId9"/>
-    <sheet sheetId="7" name="Coverage" state="visible" r:id="rId10"/>
-    <sheet sheetId="8" name="Attribute coverage" state="visible" r:id="rId11"/>
-    <sheet sheetId="9" name="Traceability by story" state="visible" r:id="rId12"/>
-    <sheet sheetId="10" name="Traceability matrix" state="visible" r:id="rId13"/>
-    <sheet sheetId="11" name="Approvals" state="visible" r:id="rId14"/>
-    <sheet sheetId="12" name="Skills" state="visible" r:id="rId15"/>
-    <sheet sheetId="13" name="Hand-overs" state="visible" r:id="rId16"/>
+    <sheet sheetId="7" name="Fixed and certified" state="visible" r:id="rId10"/>
+    <sheet sheetId="8" name="Coverage" state="visible" r:id="rId11"/>
+    <sheet sheetId="9" name="Attribute coverage" state="visible" r:id="rId12"/>
+    <sheet sheetId="10" name="Traceability by story" state="visible" r:id="rId13"/>
+    <sheet sheetId="11" name="Traceability matrix" state="visible" r:id="rId14"/>
+    <sheet sheetId="12" name="Approvals" state="visible" r:id="rId15"/>
+    <sheet sheetId="13" name="Skills" state="visible" r:id="rId16"/>
+    <sheet sheetId="14" name="Hand-overs" state="visible" r:id="rId17"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1640" uniqueCount="638">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1649" uniqueCount="641">
   <si>
     <t>Metric</t>
   </si>
@@ -115,7 +116,7 @@
     <t>Narrative</t>
   </si>
   <si>
-    <t>Hotel booking baseline · End-to-end (baseline) worked from Jira initiative AQPI-1 (Jira export on GitHub), Jira epic AQPI-2, AQPI-6, AQPI-10, AQPI-14, AQPI-18, AQPI-23, AQPI-27 (Jira export on GitHub), Codebase sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform (35af1ef) (pulled live from GitHub). The reviewed requirement set holds 128 requirements. 8 test cases are designed, 8 of them automated in 7 Playwright scripts. Execution ran 8 automated cases for real: 8 passed and 0 failed (pass rate 100%). No defects were raised.</t>
+    <t>Hotel booking baseline · End-to-end (baseline) worked from Jira initiative AQPI-1 (Jira export on GitHub), Jira epic AQPI-2, AQPI-6, AQPI-10, AQPI-14, AQPI-18, AQPI-23, AQPI-27 (Jira export on GitHub), Codebase sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform (452df41) (pulled live from GitHub). The reviewed requirement set holds 128 requirements. 8 test cases are designed, 8 of them automated in 7 Playwright scripts. Execution ran 8 automated cases for real: 8 passed and 0 failed (pass rate 100%). No defects were raised.</t>
   </si>
   <si>
     <t>Narrative drafted by</t>
@@ -163,13 +164,13 @@
     <t>Codebase</t>
   </si>
   <si>
-    <t>sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform (35af1ef)</t>
+    <t>sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform (452df41)</t>
   </si>
   <si>
     <t>github</t>
   </si>
   <si>
-    <t>Pulled live from GitHub: git clone of sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform (35af1ef) at 2026-10-02T19:44:01.743Z</t>
+    <t>Pulled live from GitHub: git clone of sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform (452df41) at 2026-10-02T20:05:08.555Z</t>
   </si>
   <si>
     <t>ID</t>
@@ -1238,6 +1239,15 @@
     <t>Movement</t>
   </si>
   <si>
+    <t>First seen</t>
+  </si>
+  <si>
+    <t>Retested in</t>
+  </si>
+  <si>
+    <t>Certification</t>
+  </si>
+  <si>
     <t>Text</t>
   </si>
   <si>
@@ -1688,7 +1698,7 @@
     <t>Priya Shah</t>
   </si>
   <si>
-    <t>2026-10-02T19:44:02.617Z</t>
+    <t>2026-10-02T20:05:09.333Z</t>
   </si>
   <si>
     <t>128 requirements approved; 0 excluded; 0 conflict(s) resolved</t>
@@ -2528,6 +2538,1146 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:K32"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="3" width="11" customWidth="1"/>
+    <col min="4" max="4" width="50" customWidth="1"/>
+    <col min="5" max="5" width="12" customWidth="1"/>
+    <col min="6" max="7" width="10" customWidth="1"/>
+    <col min="8" max="9" width="8" customWidth="1"/>
+    <col min="10" max="10" width="16" customWidth="1"/>
+    <col min="11" max="11" width="20" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="E2" s="2">
+        <v>6</v>
+      </c>
+      <c r="F2" s="2">
+        <v>7</v>
+      </c>
+      <c r="G2" s="2">
+        <v>7</v>
+      </c>
+      <c r="H2" s="2">
+        <v>7</v>
+      </c>
+      <c r="I2" s="2">
+        <v>0</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="E3" s="2">
+        <v>0</v>
+      </c>
+      <c r="F3" s="2">
+        <v>0</v>
+      </c>
+      <c r="G3" s="2">
+        <v>0</v>
+      </c>
+      <c r="H3" s="2">
+        <v>0</v>
+      </c>
+      <c r="I3" s="2">
+        <v>0</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="E4" s="2">
+        <v>0</v>
+      </c>
+      <c r="F4" s="2">
+        <v>0</v>
+      </c>
+      <c r="G4" s="2">
+        <v>0</v>
+      </c>
+      <c r="H4" s="2">
+        <v>0</v>
+      </c>
+      <c r="I4" s="2">
+        <v>0</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="E5" s="2">
+        <v>0</v>
+      </c>
+      <c r="F5" s="2">
+        <v>0</v>
+      </c>
+      <c r="G5" s="2">
+        <v>0</v>
+      </c>
+      <c r="H5" s="2">
+        <v>0</v>
+      </c>
+      <c r="I5" s="2">
+        <v>0</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="E6" s="2">
+        <v>0</v>
+      </c>
+      <c r="F6" s="2">
+        <v>0</v>
+      </c>
+      <c r="G6" s="2">
+        <v>0</v>
+      </c>
+      <c r="H6" s="2">
+        <v>0</v>
+      </c>
+      <c r="I6" s="2">
+        <v>0</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E7" s="2">
+        <v>0</v>
+      </c>
+      <c r="F7" s="2">
+        <v>0</v>
+      </c>
+      <c r="G7" s="2">
+        <v>0</v>
+      </c>
+      <c r="H7" s="2">
+        <v>0</v>
+      </c>
+      <c r="I7" s="2">
+        <v>0</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="E8" s="2">
+        <v>0</v>
+      </c>
+      <c r="F8" s="2">
+        <v>0</v>
+      </c>
+      <c r="G8" s="2">
+        <v>0</v>
+      </c>
+      <c r="H8" s="2">
+        <v>0</v>
+      </c>
+      <c r="I8" s="2">
+        <v>0</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>465</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="E9" s="2">
+        <v>0</v>
+      </c>
+      <c r="F9" s="2">
+        <v>0</v>
+      </c>
+      <c r="G9" s="2">
+        <v>0</v>
+      </c>
+      <c r="H9" s="2">
+        <v>0</v>
+      </c>
+      <c r="I9" s="2">
+        <v>0</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>468</v>
+      </c>
+      <c r="E10" s="2">
+        <v>0</v>
+      </c>
+      <c r="F10" s="2">
+        <v>0</v>
+      </c>
+      <c r="G10" s="2">
+        <v>0</v>
+      </c>
+      <c r="H10" s="2">
+        <v>0</v>
+      </c>
+      <c r="I10" s="2">
+        <v>0</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="E11" s="2">
+        <v>0</v>
+      </c>
+      <c r="F11" s="2">
+        <v>0</v>
+      </c>
+      <c r="G11" s="2">
+        <v>0</v>
+      </c>
+      <c r="H11" s="2">
+        <v>0</v>
+      </c>
+      <c r="I11" s="2">
+        <v>0</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="E12" s="2">
+        <v>0</v>
+      </c>
+      <c r="F12" s="2">
+        <v>0</v>
+      </c>
+      <c r="G12" s="2">
+        <v>0</v>
+      </c>
+      <c r="H12" s="2">
+        <v>0</v>
+      </c>
+      <c r="I12" s="2">
+        <v>0</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="E13" s="2">
+        <v>1</v>
+      </c>
+      <c r="F13" s="2">
+        <v>1</v>
+      </c>
+      <c r="G13" s="2">
+        <v>1</v>
+      </c>
+      <c r="H13" s="2">
+        <v>1</v>
+      </c>
+      <c r="I13" s="2">
+        <v>0</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>475</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="E14" s="2">
+        <v>0</v>
+      </c>
+      <c r="F14" s="2">
+        <v>0</v>
+      </c>
+      <c r="G14" s="2">
+        <v>0</v>
+      </c>
+      <c r="H14" s="2">
+        <v>0</v>
+      </c>
+      <c r="I14" s="2">
+        <v>0</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="E15" s="2">
+        <v>0</v>
+      </c>
+      <c r="F15" s="2">
+        <v>0</v>
+      </c>
+      <c r="G15" s="2">
+        <v>0</v>
+      </c>
+      <c r="H15" s="2">
+        <v>0</v>
+      </c>
+      <c r="I15" s="2">
+        <v>0</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>480</v>
+      </c>
+      <c r="E16" s="2">
+        <v>0</v>
+      </c>
+      <c r="F16" s="2">
+        <v>0</v>
+      </c>
+      <c r="G16" s="2">
+        <v>0</v>
+      </c>
+      <c r="H16" s="2">
+        <v>0</v>
+      </c>
+      <c r="I16" s="2">
+        <v>0</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="K16" s="2" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="E17" s="2">
+        <v>0</v>
+      </c>
+      <c r="F17" s="2">
+        <v>0</v>
+      </c>
+      <c r="G17" s="2">
+        <v>0</v>
+      </c>
+      <c r="H17" s="2">
+        <v>0</v>
+      </c>
+      <c r="I17" s="2">
+        <v>0</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="K17" s="2" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>484</v>
+      </c>
+      <c r="E18" s="2">
+        <v>0</v>
+      </c>
+      <c r="F18" s="2">
+        <v>0</v>
+      </c>
+      <c r="G18" s="2">
+        <v>0</v>
+      </c>
+      <c r="H18" s="2">
+        <v>0</v>
+      </c>
+      <c r="I18" s="2">
+        <v>0</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="K18" s="2" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>485</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="E19" s="2">
+        <v>0</v>
+      </c>
+      <c r="F19" s="2">
+        <v>0</v>
+      </c>
+      <c r="G19" s="2">
+        <v>0</v>
+      </c>
+      <c r="H19" s="2">
+        <v>0</v>
+      </c>
+      <c r="I19" s="2">
+        <v>0</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="K19" s="2" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>485</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="E20" s="2">
+        <v>0</v>
+      </c>
+      <c r="F20" s="2">
+        <v>0</v>
+      </c>
+      <c r="G20" s="2">
+        <v>0</v>
+      </c>
+      <c r="H20" s="2">
+        <v>0</v>
+      </c>
+      <c r="I20" s="2">
+        <v>0</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="K20" s="2" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>489</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>485</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="E21" s="2">
+        <v>0</v>
+      </c>
+      <c r="F21" s="2">
+        <v>0</v>
+      </c>
+      <c r="G21" s="2">
+        <v>0</v>
+      </c>
+      <c r="H21" s="2">
+        <v>0</v>
+      </c>
+      <c r="I21" s="2">
+        <v>0</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="K21" s="2" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>485</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="E22" s="2">
+        <v>0</v>
+      </c>
+      <c r="F22" s="2">
+        <v>0</v>
+      </c>
+      <c r="G22" s="2">
+        <v>0</v>
+      </c>
+      <c r="H22" s="2">
+        <v>0</v>
+      </c>
+      <c r="I22" s="2">
+        <v>0</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="K22" s="2" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>485</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="E23" s="2">
+        <v>0</v>
+      </c>
+      <c r="F23" s="2">
+        <v>0</v>
+      </c>
+      <c r="G23" s="2">
+        <v>0</v>
+      </c>
+      <c r="H23" s="2">
+        <v>0</v>
+      </c>
+      <c r="I23" s="2">
+        <v>0</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="K23" s="2" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="E24" s="2">
+        <v>0</v>
+      </c>
+      <c r="F24" s="2">
+        <v>0</v>
+      </c>
+      <c r="G24" s="2">
+        <v>0</v>
+      </c>
+      <c r="H24" s="2">
+        <v>0</v>
+      </c>
+      <c r="I24" s="2">
+        <v>0</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="K24" s="2" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="E25" s="2">
+        <v>0</v>
+      </c>
+      <c r="F25" s="2">
+        <v>0</v>
+      </c>
+      <c r="G25" s="2">
+        <v>0</v>
+      </c>
+      <c r="H25" s="2">
+        <v>0</v>
+      </c>
+      <c r="I25" s="2">
+        <v>0</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="K25" s="2" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>500</v>
+      </c>
+      <c r="E26" s="2">
+        <v>0</v>
+      </c>
+      <c r="F26" s="2">
+        <v>0</v>
+      </c>
+      <c r="G26" s="2">
+        <v>0</v>
+      </c>
+      <c r="H26" s="2">
+        <v>0</v>
+      </c>
+      <c r="I26" s="2">
+        <v>0</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="K26" s="2" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
+        <v>501</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="E27" s="2">
+        <v>0</v>
+      </c>
+      <c r="F27" s="2">
+        <v>0</v>
+      </c>
+      <c r="G27" s="2">
+        <v>0</v>
+      </c>
+      <c r="H27" s="2">
+        <v>0</v>
+      </c>
+      <c r="I27" s="2">
+        <v>0</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="K27" s="2" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>504</v>
+      </c>
+      <c r="E28" s="2">
+        <v>0</v>
+      </c>
+      <c r="F28" s="2">
+        <v>0</v>
+      </c>
+      <c r="G28" s="2">
+        <v>0</v>
+      </c>
+      <c r="H28" s="2">
+        <v>0</v>
+      </c>
+      <c r="I28" s="2">
+        <v>0</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="K28" s="2" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="s">
+        <v>505</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="E29" s="2">
+        <v>0</v>
+      </c>
+      <c r="F29" s="2">
+        <v>0</v>
+      </c>
+      <c r="G29" s="2">
+        <v>0</v>
+      </c>
+      <c r="H29" s="2">
+        <v>0</v>
+      </c>
+      <c r="I29" s="2">
+        <v>0</v>
+      </c>
+      <c r="J29" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="K29" s="2" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="E30" s="2">
+        <v>0</v>
+      </c>
+      <c r="F30" s="2">
+        <v>0</v>
+      </c>
+      <c r="G30" s="2">
+        <v>0</v>
+      </c>
+      <c r="H30" s="2">
+        <v>0</v>
+      </c>
+      <c r="I30" s="2">
+        <v>0</v>
+      </c>
+      <c r="J30" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="K30" s="2" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="2" t="s">
+        <v>509</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="E31" s="2">
+        <v>0</v>
+      </c>
+      <c r="F31" s="2">
+        <v>0</v>
+      </c>
+      <c r="G31" s="2">
+        <v>0</v>
+      </c>
+      <c r="H31" s="2">
+        <v>0</v>
+      </c>
+      <c r="I31" s="2">
+        <v>0</v>
+      </c>
+      <c r="J31" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="K31" s="2" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>512</v>
+      </c>
+      <c r="E32" s="2">
+        <v>0</v>
+      </c>
+      <c r="F32" s="2">
+        <v>0</v>
+      </c>
+      <c r="G32" s="2">
+        <v>0</v>
+      </c>
+      <c r="H32" s="2">
+        <v>0</v>
+      </c>
+      <c r="I32" s="2">
+        <v>0</v>
+      </c>
+      <c r="J32" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="K32" s="2" t="s">
+        <v>405</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:M9"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
@@ -2546,19 +3696,19 @@
   <sheetData>
     <row r="1" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>50</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>314</v>
@@ -2567,19 +3717,19 @@
         <v>51</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>386</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="M1" s="1" t="s">
         <v>393</v>
@@ -2596,7 +3746,7 @@
         <v>55</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>326</v>
@@ -2611,10 +3761,10 @@
         <v>337</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="K2" s="2" t="s">
         <v>389</v>
@@ -2637,7 +3787,7 @@
         <v>55</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>340</v>
@@ -2652,10 +3802,10 @@
         <v>337</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="K3" s="2" t="s">
         <v>389</v>
@@ -2678,7 +3828,7 @@
         <v>59</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>346</v>
@@ -2693,10 +3843,10 @@
         <v>337</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>389</v>
@@ -2719,7 +3869,7 @@
         <v>63</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>354</v>
@@ -2734,10 +3884,10 @@
         <v>337</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="K5" s="2" t="s">
         <v>389</v>
@@ -2760,7 +3910,7 @@
         <v>65</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>362</v>
@@ -2775,10 +3925,10 @@
         <v>337</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="K6" s="2" t="s">
         <v>389</v>
@@ -2801,7 +3951,7 @@
         <v>67</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>370</v>
@@ -2816,10 +3966,10 @@
         <v>337</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="K7" s="2" t="s">
         <v>389</v>
@@ -2842,7 +3992,7 @@
         <v>69</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>377</v>
@@ -2857,10 +4007,10 @@
         <v>337</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="K8" s="2" t="s">
         <v>389</v>
@@ -2874,7 +4024,7 @@
     </row>
     <row r="9" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>157</v>
@@ -2883,7 +4033,7 @@
         <v>158</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>383</v>
@@ -2898,10 +4048,10 @@
         <v>337</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>389</v>
@@ -2919,7 +4069,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
@@ -2933,36 +4083,36 @@
   <sheetData>
     <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
     </row>
     <row r="2" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
     </row>
   </sheetData>
@@ -2971,7 +4121,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
@@ -2985,189 +4135,189 @@
   <sheetData>
     <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>314</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
     </row>
     <row r="2" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
     </row>
     <row r="3" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
     </row>
     <row r="4" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
     </row>
     <row r="5" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>572</v>
+        <v>575</v>
       </c>
     </row>
     <row r="6" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
     </row>
     <row r="7" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
     </row>
     <row r="8" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
     </row>
     <row r="9" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
     </row>
     <row r="10" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
     </row>
     <row r="11" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>602</v>
+        <v>605</v>
       </c>
     </row>
   </sheetData>
@@ -3176,7 +4326,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
@@ -3190,186 +4340,186 @@
   <sheetData>
     <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>604</v>
+        <v>607</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
     </row>
     <row r="2" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>339</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>611</v>
+        <v>614</v>
       </c>
     </row>
     <row r="3" spans="2:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B3" s="2" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>339</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>612</v>
+        <v>615</v>
       </c>
     </row>
     <row r="4" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
+        <v>616</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>601</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>613</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>598</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>610</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>339</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>614</v>
+        <v>617</v>
       </c>
     </row>
     <row r="5" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>339</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>617</v>
+        <v>620</v>
       </c>
     </row>
     <row r="6" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>339</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>620</v>
+        <v>623</v>
       </c>
     </row>
     <row r="7" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>339</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>623</v>
+        <v>626</v>
       </c>
     </row>
     <row r="8" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>339</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>626</v>
+        <v>629</v>
       </c>
     </row>
     <row r="9" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>631</v>
+        <v>634</v>
       </c>
     </row>
     <row r="10" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>339</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>634</v>
+        <v>637</v>
       </c>
     </row>
     <row r="11" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>339</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>637</v>
+        <v>640</v>
       </c>
     </row>
   </sheetData>
@@ -6304,7 +7454,7 @@
         <v>389</v>
       </c>
       <c r="E2" s="2">
-        <v>1160</v>
+        <v>1148</v>
       </c>
       <c r="F2" s="2"/>
     </row>
@@ -6322,7 +7472,7 @@
         <v>389</v>
       </c>
       <c r="E3" s="2">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="F3" s="2"/>
     </row>
@@ -6340,7 +7490,7 @@
         <v>389</v>
       </c>
       <c r="E4" s="2">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="F4" s="2"/>
     </row>
@@ -6358,7 +7508,7 @@
         <v>389</v>
       </c>
       <c r="E5" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="F5" s="2"/>
     </row>
@@ -6394,7 +7544,7 @@
         <v>389</v>
       </c>
       <c r="E7" s="2">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="F7" s="2"/>
     </row>
@@ -6412,7 +7562,7 @@
         <v>389</v>
       </c>
       <c r="E8" s="2">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="F8" s="2"/>
     </row>
@@ -6430,7 +7580,7 @@
         <v>389</v>
       </c>
       <c r="E9" s="2">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="F9" s="2"/>
     </row>
@@ -6498,6 +7648,53 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:I1"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="2" max="2" width="50" customWidth="1"/>
+    <col min="3" max="3" width="11" customWidth="1"/>
+    <col min="4" max="4" width="10" customWidth="1"/>
+    <col min="5" max="6" width="11" customWidth="1"/>
+    <col min="9" max="9" width="80" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>400</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G129"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
@@ -6514,16 +7711,16 @@
         <v>50</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>337</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>23</v>
@@ -6552,7 +7749,7 @@
         <v>0</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
     </row>
     <row r="3" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6575,7 +7772,7 @@
         <v>0</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
     </row>
     <row r="4" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6598,7 +7795,7 @@
         <v>0</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="5" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6621,7 +7818,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
     </row>
     <row r="6" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6644,7 +7841,7 @@
         <v>0</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
     </row>
     <row r="7" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6667,7 +7864,7 @@
         <v>0</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
     </row>
     <row r="8" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6690,7 +7887,7 @@
         <v>0</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
     </row>
     <row r="9" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6713,7 +7910,7 @@
         <v>0</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="10" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6736,7 +7933,7 @@
         <v>0</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="11" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6759,7 +7956,7 @@
         <v>0</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="12" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6782,7 +7979,7 @@
         <v>0</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="13" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6805,7 +8002,7 @@
         <v>0</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="14" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6828,7 +8025,7 @@
         <v>0</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="15" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6851,7 +8048,7 @@
         <v>0</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="16" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6874,7 +8071,7 @@
         <v>0</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="17" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6897,7 +8094,7 @@
         <v>0</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="18" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6920,7 +8117,7 @@
         <v>0</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="19" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6943,7 +8140,7 @@
         <v>0</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="20" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6966,7 +8163,7 @@
         <v>0</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="21" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6989,7 +8186,7 @@
         <v>0</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="22" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7012,7 +8209,7 @@
         <v>0</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="23" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7035,7 +8232,7 @@
         <v>0</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="24" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7058,7 +8255,7 @@
         <v>0</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="25" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7081,7 +8278,7 @@
         <v>0</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="26" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7104,7 +8301,7 @@
         <v>0</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="27" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7127,7 +8324,7 @@
         <v>0</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="28" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7150,7 +8347,7 @@
         <v>0</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="29" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7173,7 +8370,7 @@
         <v>0</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="30" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7196,7 +8393,7 @@
         <v>0</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="31" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7219,7 +8416,7 @@
         <v>0</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="32" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7242,7 +8439,7 @@
         <v>0</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="33" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7265,7 +8462,7 @@
         <v>0</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="34" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7288,7 +8485,7 @@
         <v>0</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="35" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7311,7 +8508,7 @@
         <v>0</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="36" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7334,7 +8531,7 @@
         <v>0</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="37" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7357,7 +8554,7 @@
         <v>0</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="38" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7380,7 +8577,7 @@
         <v>0</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="39" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7403,7 +8600,7 @@
         <v>0</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="40" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7426,7 +8623,7 @@
         <v>0</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="41" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7449,7 +8646,7 @@
         <v>0</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="42" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7472,7 +8669,7 @@
         <v>0</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="43" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7495,7 +8692,7 @@
         <v>0</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="44" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7518,7 +8715,7 @@
         <v>0</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="45" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7541,7 +8738,7 @@
         <v>0</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="46" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7564,7 +8761,7 @@
         <v>0</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="47" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7587,7 +8784,7 @@
         <v>0</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="48" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7610,7 +8807,7 @@
         <v>0</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="49" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7633,7 +8830,7 @@
         <v>0</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="50" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7656,7 +8853,7 @@
         <v>0</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="51" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7679,7 +8876,7 @@
         <v>0</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="52" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7702,7 +8899,7 @@
         <v>0</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
     </row>
     <row r="53" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7725,7 +8922,7 @@
         <v>0</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="54" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7748,7 +8945,7 @@
         <v>0</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="55" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7771,7 +8968,7 @@
         <v>0</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="56" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7794,7 +8991,7 @@
         <v>0</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="57" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7817,7 +9014,7 @@
         <v>0</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="58" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7840,7 +9037,7 @@
         <v>0</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="59" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7863,7 +9060,7 @@
         <v>0</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="60" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7886,7 +9083,7 @@
         <v>0</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="61" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7909,7 +9106,7 @@
         <v>0</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="62" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7932,7 +9129,7 @@
         <v>0</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="63" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7955,7 +9152,7 @@
         <v>0</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="64" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7978,7 +9175,7 @@
         <v>0</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="65" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8001,7 +9198,7 @@
         <v>0</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="66" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8024,7 +9221,7 @@
         <v>0</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="67" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8047,7 +9244,7 @@
         <v>0</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="68" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8070,7 +9267,7 @@
         <v>0</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="69" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8093,7 +9290,7 @@
         <v>0</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="70" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8116,7 +9313,7 @@
         <v>0</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="71" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8139,7 +9336,7 @@
         <v>0</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="72" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8162,7 +9359,7 @@
         <v>0</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="73" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8185,7 +9382,7 @@
         <v>0</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="74" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8208,7 +9405,7 @@
         <v>0</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="75" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8231,7 +9428,7 @@
         <v>0</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="76" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8254,7 +9451,7 @@
         <v>0</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="77" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8277,7 +9474,7 @@
         <v>0</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="78" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8300,7 +9497,7 @@
         <v>0</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="79" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8323,7 +9520,7 @@
         <v>0</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="80" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8346,7 +9543,7 @@
         <v>0</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="81" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8369,7 +9566,7 @@
         <v>0</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="82" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8392,7 +9589,7 @@
         <v>0</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="83" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8415,7 +9612,7 @@
         <v>0</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="84" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8438,7 +9635,7 @@
         <v>0</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="85" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8461,7 +9658,7 @@
         <v>0</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="86" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8484,7 +9681,7 @@
         <v>0</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="87" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8507,7 +9704,7 @@
         <v>0</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="88" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8530,7 +9727,7 @@
         <v>0</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="89" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8553,7 +9750,7 @@
         <v>0</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="90" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8576,7 +9773,7 @@
         <v>0</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="91" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8599,7 +9796,7 @@
         <v>0</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="92" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8622,7 +9819,7 @@
         <v>0</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="93" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8645,7 +9842,7 @@
         <v>0</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="94" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8668,7 +9865,7 @@
         <v>0</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="95" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8691,7 +9888,7 @@
         <v>0</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="96" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8714,7 +9911,7 @@
         <v>0</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="97" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8737,7 +9934,7 @@
         <v>0</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="98" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8760,7 +9957,7 @@
         <v>0</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="99" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8783,7 +9980,7 @@
         <v>0</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="100" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8806,7 +10003,7 @@
         <v>0</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="101" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8829,7 +10026,7 @@
         <v>0</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="102" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8852,7 +10049,7 @@
         <v>0</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="103" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8875,7 +10072,7 @@
         <v>0</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="104" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8898,7 +10095,7 @@
         <v>0</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="105" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8921,7 +10118,7 @@
         <v>0</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="106" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8944,7 +10141,7 @@
         <v>0</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="107" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8967,7 +10164,7 @@
         <v>0</v>
       </c>
       <c r="G107" s="2" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="108" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8990,7 +10187,7 @@
         <v>0</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="109" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9013,7 +10210,7 @@
         <v>0</v>
       </c>
       <c r="G109" s="2" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="110" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9036,7 +10233,7 @@
         <v>0</v>
       </c>
       <c r="G110" s="2" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="111" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9059,7 +10256,7 @@
         <v>0</v>
       </c>
       <c r="G111" s="2" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="112" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9082,7 +10279,7 @@
         <v>0</v>
       </c>
       <c r="G112" s="2" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="113" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9105,7 +10302,7 @@
         <v>0</v>
       </c>
       <c r="G113" s="2" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="114" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9128,7 +10325,7 @@
         <v>0</v>
       </c>
       <c r="G114" s="2" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="115" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9151,7 +10348,7 @@
         <v>0</v>
       </c>
       <c r="G115" s="2" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="116" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9174,7 +10371,7 @@
         <v>0</v>
       </c>
       <c r="G116" s="2" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="117" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9197,7 +10394,7 @@
         <v>0</v>
       </c>
       <c r="G117" s="2" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="118" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9220,7 +10417,7 @@
         <v>0</v>
       </c>
       <c r="G118" s="2" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="119" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9243,7 +10440,7 @@
         <v>0</v>
       </c>
       <c r="G119" s="2" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="120" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9266,7 +10463,7 @@
         <v>0</v>
       </c>
       <c r="G120" s="2" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="121" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9289,7 +10486,7 @@
         <v>0</v>
       </c>
       <c r="G121" s="2" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="122" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9312,7 +10509,7 @@
         <v>0</v>
       </c>
       <c r="G122" s="2" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="123" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9335,7 +10532,7 @@
         <v>0</v>
       </c>
       <c r="G123" s="2" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="124" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9358,7 +10555,7 @@
         <v>0</v>
       </c>
       <c r="G124" s="2" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="125" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9381,7 +10578,7 @@
         <v>0</v>
       </c>
       <c r="G125" s="2" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="126" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9404,7 +10601,7 @@
         <v>0</v>
       </c>
       <c r="G126" s="2" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="127" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9427,7 +10624,7 @@
         <v>0</v>
       </c>
       <c r="G127" s="2" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="128" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9450,7 +10647,7 @@
         <v>0</v>
       </c>
       <c r="G128" s="2" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="129" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9473,7 +10670,7 @@
         <v>0</v>
       </c>
       <c r="G129" s="2" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
   </sheetData>
@@ -9482,7 +10679,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D16"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
@@ -9495,13 +10692,13 @@
   <sheetData>
     <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>6</v>
@@ -9509,1352 +10706,212 @@
     </row>
     <row r="2" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
     </row>
     <row r="3" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>339</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
     </row>
     <row r="4" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>339</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
     </row>
     <row r="5" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>339</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
     </row>
     <row r="6" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>339</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
     </row>
     <row r="7" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>339</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
     </row>
     <row r="8" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
     </row>
     <row r="9" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>340</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
     </row>
     <row r="10" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
     </row>
     <row r="11" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
     </row>
     <row r="12" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>339</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
     </row>
     <row r="13" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>339</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
     </row>
     <row r="14" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>339</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
     </row>
     <row r="15" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>339</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
     </row>
     <row r="16" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>362</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>409</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K32"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
-  <cols>
-    <col min="1" max="3" width="11" customWidth="1"/>
-    <col min="4" max="4" width="50" customWidth="1"/>
-    <col min="5" max="5" width="12" customWidth="1"/>
-    <col min="6" max="7" width="10" customWidth="1"/>
-    <col min="8" max="9" width="8" customWidth="1"/>
-    <col min="10" max="10" width="16" customWidth="1"/>
-    <col min="11" max="11" width="20" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>441</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>442</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>443</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>444</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>337</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>445</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>446</v>
-      </c>
-      <c r="E2" s="2">
-        <v>6</v>
-      </c>
-      <c r="F2" s="2">
-        <v>7</v>
-      </c>
-      <c r="G2" s="2">
-        <v>7</v>
-      </c>
-      <c r="H2" s="2">
-        <v>7</v>
-      </c>
-      <c r="I2" s="2">
-        <v>0</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>448</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>449</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>450</v>
-      </c>
-      <c r="E3" s="2">
-        <v>0</v>
-      </c>
-      <c r="F3" s="2">
-        <v>0</v>
-      </c>
-      <c r="G3" s="2">
-        <v>0</v>
-      </c>
-      <c r="H3" s="2">
-        <v>0</v>
-      </c>
-      <c r="I3" s="2">
-        <v>0</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>451</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>452</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>448</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>453</v>
-      </c>
-      <c r="E4" s="2">
-        <v>0</v>
-      </c>
-      <c r="F4" s="2">
-        <v>0</v>
-      </c>
-      <c r="G4" s="2">
-        <v>0</v>
-      </c>
-      <c r="H4" s="2">
-        <v>0</v>
-      </c>
-      <c r="I4" s="2">
-        <v>0</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>454</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>452</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>448</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>455</v>
-      </c>
-      <c r="E5" s="2">
-        <v>0</v>
-      </c>
-      <c r="F5" s="2">
-        <v>0</v>
-      </c>
-      <c r="G5" s="2">
-        <v>0</v>
-      </c>
-      <c r="H5" s="2">
-        <v>0</v>
-      </c>
-      <c r="I5" s="2">
-        <v>0</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>456</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>452</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>448</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>457</v>
-      </c>
-      <c r="E6" s="2">
-        <v>0</v>
-      </c>
-      <c r="F6" s="2">
-        <v>0</v>
-      </c>
-      <c r="G6" s="2">
-        <v>0</v>
-      </c>
-      <c r="H6" s="2">
-        <v>0</v>
-      </c>
-      <c r="I6" s="2">
-        <v>0</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>449</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>459</v>
-      </c>
-      <c r="E7" s="2">
-        <v>0</v>
-      </c>
-      <c r="F7" s="2">
-        <v>0</v>
-      </c>
-      <c r="G7" s="2">
-        <v>0</v>
-      </c>
-      <c r="H7" s="2">
-        <v>0</v>
-      </c>
-      <c r="I7" s="2">
-        <v>0</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="K7" s="2" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>460</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>452</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>461</v>
-      </c>
-      <c r="E8" s="2">
-        <v>0</v>
-      </c>
-      <c r="F8" s="2">
-        <v>0</v>
-      </c>
-      <c r="G8" s="2">
-        <v>0</v>
-      </c>
-      <c r="H8" s="2">
-        <v>0</v>
-      </c>
-      <c r="I8" s="2">
-        <v>0</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>452</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>463</v>
-      </c>
-      <c r="E9" s="2">
-        <v>0</v>
-      </c>
-      <c r="F9" s="2">
-        <v>0</v>
-      </c>
-      <c r="G9" s="2">
-        <v>0</v>
-      </c>
-      <c r="H9" s="2">
-        <v>0</v>
-      </c>
-      <c r="I9" s="2">
-        <v>0</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>464</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>452</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>465</v>
-      </c>
-      <c r="E10" s="2">
-        <v>0</v>
-      </c>
-      <c r="F10" s="2">
-        <v>0</v>
-      </c>
-      <c r="G10" s="2">
-        <v>0</v>
-      </c>
-      <c r="H10" s="2">
-        <v>0</v>
-      </c>
-      <c r="I10" s="2">
-        <v>0</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="K10" s="2" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>466</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>449</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>467</v>
-      </c>
-      <c r="E11" s="2">
-        <v>0</v>
-      </c>
-      <c r="F11" s="2">
-        <v>0</v>
-      </c>
-      <c r="G11" s="2">
-        <v>0</v>
-      </c>
-      <c r="H11" s="2">
-        <v>0</v>
-      </c>
-      <c r="I11" s="2">
-        <v>0</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="K11" s="2" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
-        <v>468</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>452</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>466</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>469</v>
-      </c>
-      <c r="E12" s="2">
-        <v>0</v>
-      </c>
-      <c r="F12" s="2">
-        <v>0</v>
-      </c>
-      <c r="G12" s="2">
-        <v>0</v>
-      </c>
-      <c r="H12" s="2">
-        <v>0</v>
-      </c>
-      <c r="I12" s="2">
-        <v>0</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="K12" s="2" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
-        <v>470</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>452</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>466</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>471</v>
-      </c>
-      <c r="E13" s="2">
-        <v>1</v>
-      </c>
-      <c r="F13" s="2">
-        <v>1</v>
-      </c>
-      <c r="G13" s="2">
-        <v>1</v>
-      </c>
-      <c r="H13" s="2">
-        <v>1</v>
-      </c>
-      <c r="I13" s="2">
-        <v>0</v>
-      </c>
-      <c r="J13" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="K13" s="2" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
-        <v>472</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>452</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>466</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>473</v>
-      </c>
-      <c r="E14" s="2">
-        <v>0</v>
-      </c>
-      <c r="F14" s="2">
-        <v>0</v>
-      </c>
-      <c r="G14" s="2">
-        <v>0</v>
-      </c>
-      <c r="H14" s="2">
-        <v>0</v>
-      </c>
-      <c r="I14" s="2">
-        <v>0</v>
-      </c>
-      <c r="J14" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="K14" s="2" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
-        <v>474</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>449</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>475</v>
-      </c>
-      <c r="E15" s="2">
-        <v>0</v>
-      </c>
-      <c r="F15" s="2">
-        <v>0</v>
-      </c>
-      <c r="G15" s="2">
-        <v>0</v>
-      </c>
-      <c r="H15" s="2">
-        <v>0</v>
-      </c>
-      <c r="I15" s="2">
-        <v>0</v>
-      </c>
-      <c r="J15" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="K15" s="2" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
-        <v>476</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>452</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>474</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>477</v>
-      </c>
-      <c r="E16" s="2">
-        <v>0</v>
-      </c>
-      <c r="F16" s="2">
-        <v>0</v>
-      </c>
-      <c r="G16" s="2">
-        <v>0</v>
-      </c>
-      <c r="H16" s="2">
-        <v>0</v>
-      </c>
-      <c r="I16" s="2">
-        <v>0</v>
-      </c>
-      <c r="J16" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="K16" s="2" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
-        <v>478</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>452</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>474</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>479</v>
-      </c>
-      <c r="E17" s="2">
-        <v>0</v>
-      </c>
-      <c r="F17" s="2">
-        <v>0</v>
-      </c>
-      <c r="G17" s="2">
-        <v>0</v>
-      </c>
-      <c r="H17" s="2">
-        <v>0</v>
-      </c>
-      <c r="I17" s="2">
-        <v>0</v>
-      </c>
-      <c r="J17" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="K17" s="2" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="2" t="s">
-        <v>480</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>452</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>474</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>481</v>
-      </c>
-      <c r="E18" s="2">
-        <v>0</v>
-      </c>
-      <c r="F18" s="2">
-        <v>0</v>
-      </c>
-      <c r="G18" s="2">
-        <v>0</v>
-      </c>
-      <c r="H18" s="2">
-        <v>0</v>
-      </c>
-      <c r="I18" s="2">
-        <v>0</v>
-      </c>
-      <c r="J18" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="K18" s="2" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="s">
-        <v>482</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>449</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>483</v>
-      </c>
-      <c r="E19" s="2">
-        <v>0</v>
-      </c>
-      <c r="F19" s="2">
-        <v>0</v>
-      </c>
-      <c r="G19" s="2">
-        <v>0</v>
-      </c>
-      <c r="H19" s="2">
-        <v>0</v>
-      </c>
-      <c r="I19" s="2">
-        <v>0</v>
-      </c>
-      <c r="J19" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="K19" s="2" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="2" t="s">
-        <v>484</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>452</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>482</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>485</v>
-      </c>
-      <c r="E20" s="2">
-        <v>0</v>
-      </c>
-      <c r="F20" s="2">
-        <v>0</v>
-      </c>
-      <c r="G20" s="2">
-        <v>0</v>
-      </c>
-      <c r="H20" s="2">
-        <v>0</v>
-      </c>
-      <c r="I20" s="2">
-        <v>0</v>
-      </c>
-      <c r="J20" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="K20" s="2" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="2" t="s">
-        <v>486</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>452</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>482</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>487</v>
-      </c>
-      <c r="E21" s="2">
-        <v>0</v>
-      </c>
-      <c r="F21" s="2">
-        <v>0</v>
-      </c>
-      <c r="G21" s="2">
-        <v>0</v>
-      </c>
-      <c r="H21" s="2">
-        <v>0</v>
-      </c>
-      <c r="I21" s="2">
-        <v>0</v>
-      </c>
-      <c r="J21" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="K21" s="2" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="2" t="s">
-        <v>488</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>452</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>482</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>489</v>
-      </c>
-      <c r="E22" s="2">
-        <v>0</v>
-      </c>
-      <c r="F22" s="2">
-        <v>0</v>
-      </c>
-      <c r="G22" s="2">
-        <v>0</v>
-      </c>
-      <c r="H22" s="2">
-        <v>0</v>
-      </c>
-      <c r="I22" s="2">
-        <v>0</v>
-      </c>
-      <c r="J22" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="K22" s="2" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="2" t="s">
-        <v>490</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>452</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>482</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>491</v>
-      </c>
-      <c r="E23" s="2">
-        <v>0</v>
-      </c>
-      <c r="F23" s="2">
-        <v>0</v>
-      </c>
-      <c r="G23" s="2">
-        <v>0</v>
-      </c>
-      <c r="H23" s="2">
-        <v>0</v>
-      </c>
-      <c r="I23" s="2">
-        <v>0</v>
-      </c>
-      <c r="J23" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="K23" s="2" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="2" t="s">
-        <v>492</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>449</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>493</v>
-      </c>
-      <c r="E24" s="2">
-        <v>0</v>
-      </c>
-      <c r="F24" s="2">
-        <v>0</v>
-      </c>
-      <c r="G24" s="2">
-        <v>0</v>
-      </c>
-      <c r="H24" s="2">
-        <v>0</v>
-      </c>
-      <c r="I24" s="2">
-        <v>0</v>
-      </c>
-      <c r="J24" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="K24" s="2" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="2" t="s">
-        <v>494</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>452</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>492</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>495</v>
-      </c>
-      <c r="E25" s="2">
-        <v>0</v>
-      </c>
-      <c r="F25" s="2">
-        <v>0</v>
-      </c>
-      <c r="G25" s="2">
-        <v>0</v>
-      </c>
-      <c r="H25" s="2">
-        <v>0</v>
-      </c>
-      <c r="I25" s="2">
-        <v>0</v>
-      </c>
-      <c r="J25" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="K25" s="2" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="2" t="s">
-        <v>496</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>452</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>492</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>497</v>
-      </c>
-      <c r="E26" s="2">
-        <v>0</v>
-      </c>
-      <c r="F26" s="2">
-        <v>0</v>
-      </c>
-      <c r="G26" s="2">
-        <v>0</v>
-      </c>
-      <c r="H26" s="2">
-        <v>0</v>
-      </c>
-      <c r="I26" s="2">
-        <v>0</v>
-      </c>
-      <c r="J26" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="K26" s="2" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="2" t="s">
-        <v>498</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>452</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>492</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>499</v>
-      </c>
-      <c r="E27" s="2">
-        <v>0</v>
-      </c>
-      <c r="F27" s="2">
-        <v>0</v>
-      </c>
-      <c r="G27" s="2">
-        <v>0</v>
-      </c>
-      <c r="H27" s="2">
-        <v>0</v>
-      </c>
-      <c r="I27" s="2">
-        <v>0</v>
-      </c>
-      <c r="J27" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="K27" s="2" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="2" t="s">
-        <v>500</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>449</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>501</v>
-      </c>
-      <c r="E28" s="2">
-        <v>0</v>
-      </c>
-      <c r="F28" s="2">
-        <v>0</v>
-      </c>
-      <c r="G28" s="2">
-        <v>0</v>
-      </c>
-      <c r="H28" s="2">
-        <v>0</v>
-      </c>
-      <c r="I28" s="2">
-        <v>0</v>
-      </c>
-      <c r="J28" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="K28" s="2" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="2" t="s">
-        <v>502</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>452</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>500</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>503</v>
-      </c>
-      <c r="E29" s="2">
-        <v>0</v>
-      </c>
-      <c r="F29" s="2">
-        <v>0</v>
-      </c>
-      <c r="G29" s="2">
-        <v>0</v>
-      </c>
-      <c r="H29" s="2">
-        <v>0</v>
-      </c>
-      <c r="I29" s="2">
-        <v>0</v>
-      </c>
-      <c r="J29" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="K29" s="2" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="2" t="s">
-        <v>504</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>452</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>500</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>505</v>
-      </c>
-      <c r="E30" s="2">
-        <v>0</v>
-      </c>
-      <c r="F30" s="2">
-        <v>0</v>
-      </c>
-      <c r="G30" s="2">
-        <v>0</v>
-      </c>
-      <c r="H30" s="2">
-        <v>0</v>
-      </c>
-      <c r="I30" s="2">
-        <v>0</v>
-      </c>
-      <c r="J30" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="K30" s="2" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="2" t="s">
-        <v>506</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>452</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>500</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>507</v>
-      </c>
-      <c r="E31" s="2">
-        <v>0</v>
-      </c>
-      <c r="F31" s="2">
-        <v>0</v>
-      </c>
-      <c r="G31" s="2">
-        <v>0</v>
-      </c>
-      <c r="H31" s="2">
-        <v>0</v>
-      </c>
-      <c r="I31" s="2">
-        <v>0</v>
-      </c>
-      <c r="J31" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="K31" s="2" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="2" t="s">
-        <v>508</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>452</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>500</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>509</v>
-      </c>
-      <c r="E32" s="2">
-        <v>0</v>
-      </c>
-      <c r="F32" s="2">
-        <v>0</v>
-      </c>
-      <c r="G32" s="2">
-        <v>0</v>
-      </c>
-      <c r="H32" s="2">
-        <v>0</v>
-      </c>
-      <c r="I32" s="2">
-        <v>0</v>
-      </c>
-      <c r="J32" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="K32" s="2" t="s">
-        <v>402</v>
+        <v>412</v>
       </c>
     </row>
   </sheetData>

--- a/agentic-qe-mvp/demo-artifacts/flow-1-hotel-e2e-CYC-3/09-report/CYC-3-cycle-report.xlsx
+++ b/agentic-qe-mvp/demo-artifacts/flow-1-hotel-e2e-CYC-3/09-report/CYC-3-cycle-report.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1649" uniqueCount="641">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1681" uniqueCount="643">
   <si>
     <t>Metric</t>
   </si>
@@ -170,7 +170,7 @@
     <t>github</t>
   </si>
   <si>
-    <t>Pulled live from GitHub: git clone of sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform (452df41) at 2026-10-02T20:05:08.555Z</t>
+    <t>Pulled live from GitHub: git clone of sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform (452df41) at 2026-10-02T20:26:12.623Z</t>
   </si>
   <si>
     <t>ID</t>
@@ -1383,6 +1383,9 @@
     <t>Level</t>
   </si>
   <si>
+    <t>Scope</t>
+  </si>
+  <si>
     <t>Parent</t>
   </si>
   <si>
@@ -1392,6 +1395,9 @@
     <t>initiative</t>
   </si>
   <si>
+    <t>this cycle</t>
+  </si>
+  <si>
     <t>[Initiative] Intelligent Hotel Shopping and Reservation Experience</t>
   </si>
   <si>
@@ -1698,7 +1704,7 @@
     <t>Priya Shah</t>
   </si>
   <si>
-    <t>2026-10-02T20:05:09.333Z</t>
+    <t>2026-10-02T20:26:13.414Z</t>
   </si>
   <si>
     <t>128 requirements approved; 0 excluded; 0 conflict(s) resolved</t>
@@ -2538,19 +2544,19 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K32"/>
+  <dimension ref="A1:L32"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="3" width="11" customWidth="1"/>
-    <col min="4" max="4" width="50" customWidth="1"/>
-    <col min="5" max="5" width="12" customWidth="1"/>
-    <col min="6" max="7" width="10" customWidth="1"/>
-    <col min="8" max="9" width="8" customWidth="1"/>
-    <col min="10" max="10" width="16" customWidth="1"/>
-    <col min="11" max="11" width="20" customWidth="1"/>
+    <col min="1" max="4" width="11" customWidth="1"/>
+    <col min="5" max="5" width="50" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
+    <col min="7" max="8" width="10" customWidth="1"/>
+    <col min="9" max="10" width="8" customWidth="1"/>
+    <col min="11" max="11" width="16" customWidth="1"/>
+    <col min="12" max="12" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>444</v>
       </c>
@@ -2564,45 +2570,48 @@
         <v>447</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>39</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>339</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>449</v>
-      </c>
-      <c r="E2" s="2">
+      <c r="E2" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="F2" s="2">
         <v>6</v>
-      </c>
-      <c r="F2" s="2">
-        <v>7</v>
       </c>
       <c r="G2" s="2">
         <v>7</v>
@@ -2611,1062 +2620,1155 @@
         <v>7</v>
       </c>
       <c r="I2" s="2">
-        <v>0</v>
-      </c>
-      <c r="J2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J2" s="2">
+        <v>0</v>
+      </c>
+      <c r="K2" s="2" t="s">
         <v>339</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="L2" s="2" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>450</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>451</v>
-      </c>
-      <c r="B3" s="2" t="s">
+      <c r="D3" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="F3" s="2">
+        <v>0</v>
+      </c>
+      <c r="G3" s="2">
+        <v>0</v>
+      </c>
+      <c r="H3" s="2">
+        <v>0</v>
+      </c>
+      <c r="I3" s="2">
+        <v>0</v>
+      </c>
+      <c r="J3" s="2">
+        <v>0</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="F4" s="2">
+        <v>0</v>
+      </c>
+      <c r="G4" s="2">
+        <v>0</v>
+      </c>
+      <c r="H4" s="2">
+        <v>0</v>
+      </c>
+      <c r="I4" s="2">
+        <v>0</v>
+      </c>
+      <c r="J4" s="2">
+        <v>0</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="F5" s="2">
+        <v>0</v>
+      </c>
+      <c r="G5" s="2">
+        <v>0</v>
+      </c>
+      <c r="H5" s="2">
+        <v>0</v>
+      </c>
+      <c r="I5" s="2">
+        <v>0</v>
+      </c>
+      <c r="J5" s="2">
+        <v>0</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="F6" s="2">
+        <v>0</v>
+      </c>
+      <c r="G6" s="2">
+        <v>0</v>
+      </c>
+      <c r="H6" s="2">
+        <v>0</v>
+      </c>
+      <c r="I6" s="2">
+        <v>0</v>
+      </c>
+      <c r="J6" s="2">
+        <v>0</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="F7" s="2">
+        <v>0</v>
+      </c>
+      <c r="G7" s="2">
+        <v>0</v>
+      </c>
+      <c r="H7" s="2">
+        <v>0</v>
+      </c>
+      <c r="I7" s="2">
+        <v>0</v>
+      </c>
+      <c r="J7" s="2">
+        <v>0</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="L7" s="2" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>465</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="F8" s="2">
+        <v>0</v>
+      </c>
+      <c r="G8" s="2">
+        <v>0</v>
+      </c>
+      <c r="H8" s="2">
+        <v>0</v>
+      </c>
+      <c r="I8" s="2">
+        <v>0</v>
+      </c>
+      <c r="J8" s="2">
+        <v>0</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>468</v>
+      </c>
+      <c r="F9" s="2">
+        <v>0</v>
+      </c>
+      <c r="G9" s="2">
+        <v>0</v>
+      </c>
+      <c r="H9" s="2">
+        <v>0</v>
+      </c>
+      <c r="I9" s="2">
+        <v>0</v>
+      </c>
+      <c r="J9" s="2">
+        <v>0</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="F10" s="2">
+        <v>0</v>
+      </c>
+      <c r="G10" s="2">
+        <v>0</v>
+      </c>
+      <c r="H10" s="2">
+        <v>0</v>
+      </c>
+      <c r="I10" s="2">
+        <v>0</v>
+      </c>
+      <c r="J10" s="2">
+        <v>0</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="L10" s="2" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="F11" s="2">
+        <v>0</v>
+      </c>
+      <c r="G11" s="2">
+        <v>0</v>
+      </c>
+      <c r="H11" s="2">
+        <v>0</v>
+      </c>
+      <c r="I11" s="2">
+        <v>0</v>
+      </c>
+      <c r="J11" s="2">
+        <v>0</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="L11" s="2" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="F12" s="2">
+        <v>0</v>
+      </c>
+      <c r="G12" s="2">
+        <v>0</v>
+      </c>
+      <c r="H12" s="2">
+        <v>0</v>
+      </c>
+      <c r="I12" s="2">
+        <v>0</v>
+      </c>
+      <c r="J12" s="2">
+        <v>0</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>475</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="F13" s="2">
+        <v>1</v>
+      </c>
+      <c r="G13" s="2">
+        <v>1</v>
+      </c>
+      <c r="H13" s="2">
+        <v>1</v>
+      </c>
+      <c r="I13" s="2">
+        <v>1</v>
+      </c>
+      <c r="J13" s="2">
+        <v>0</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="L13" s="2" t="s">
         <v>452</v>
       </c>
-      <c r="C3" s="2" t="s">
+    </row>
+    <row r="14" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="F14" s="2">
+        <v>0</v>
+      </c>
+      <c r="G14" s="2">
+        <v>0</v>
+      </c>
+      <c r="H14" s="2">
+        <v>0</v>
+      </c>
+      <c r="I14" s="2">
+        <v>0</v>
+      </c>
+      <c r="J14" s="2">
+        <v>0</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="L14" s="2" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="D15" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>453</v>
-      </c>
-      <c r="E3" s="2">
-        <v>0</v>
-      </c>
-      <c r="F3" s="2">
-        <v>0</v>
-      </c>
-      <c r="G3" s="2">
-        <v>0</v>
-      </c>
-      <c r="H3" s="2">
-        <v>0</v>
-      </c>
-      <c r="I3" s="2">
-        <v>0</v>
-      </c>
-      <c r="J3" s="2" t="s">
+      <c r="E15" s="2" t="s">
+        <v>480</v>
+      </c>
+      <c r="F15" s="2">
+        <v>0</v>
+      </c>
+      <c r="G15" s="2">
+        <v>0</v>
+      </c>
+      <c r="H15" s="2">
+        <v>0</v>
+      </c>
+      <c r="I15" s="2">
+        <v>0</v>
+      </c>
+      <c r="J15" s="2">
+        <v>0</v>
+      </c>
+      <c r="K15" s="2" t="s">
         <v>339</v>
       </c>
-      <c r="K3" s="2" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
+      <c r="L15" s="2" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="F16" s="2">
+        <v>0</v>
+      </c>
+      <c r="G16" s="2">
+        <v>0</v>
+      </c>
+      <c r="H16" s="2">
+        <v>0</v>
+      </c>
+      <c r="I16" s="2">
+        <v>0</v>
+      </c>
+      <c r="J16" s="2">
+        <v>0</v>
+      </c>
+      <c r="K16" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="L16" s="2" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>484</v>
+      </c>
+      <c r="F17" s="2">
+        <v>0</v>
+      </c>
+      <c r="G17" s="2">
+        <v>0</v>
+      </c>
+      <c r="H17" s="2">
+        <v>0</v>
+      </c>
+      <c r="I17" s="2">
+        <v>0</v>
+      </c>
+      <c r="J17" s="2">
+        <v>0</v>
+      </c>
+      <c r="K17" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="L17" s="2" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>485</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="F18" s="2">
+        <v>0</v>
+      </c>
+      <c r="G18" s="2">
+        <v>0</v>
+      </c>
+      <c r="H18" s="2">
+        <v>0</v>
+      </c>
+      <c r="I18" s="2">
+        <v>0</v>
+      </c>
+      <c r="J18" s="2">
+        <v>0</v>
+      </c>
+      <c r="K18" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="L18" s="2" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="B19" s="2" t="s">
         <v>454</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>455</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>451</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>456</v>
-      </c>
-      <c r="E4" s="2">
-        <v>0</v>
-      </c>
-      <c r="F4" s="2">
-        <v>0</v>
-      </c>
-      <c r="G4" s="2">
-        <v>0</v>
-      </c>
-      <c r="H4" s="2">
-        <v>0</v>
-      </c>
-      <c r="I4" s="2">
-        <v>0</v>
-      </c>
-      <c r="J4" s="2" t="s">
+      <c r="C19" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="F19" s="2">
+        <v>0</v>
+      </c>
+      <c r="G19" s="2">
+        <v>0</v>
+      </c>
+      <c r="H19" s="2">
+        <v>0</v>
+      </c>
+      <c r="I19" s="2">
+        <v>0</v>
+      </c>
+      <c r="J19" s="2">
+        <v>0</v>
+      </c>
+      <c r="K19" s="2" t="s">
         <v>339</v>
       </c>
-      <c r="K4" s="2" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
+      <c r="L19" s="2" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>489</v>
+      </c>
+      <c r="B20" s="2" t="s">
         <v>457</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>455</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>451</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="E5" s="2">
-        <v>0</v>
-      </c>
-      <c r="F5" s="2">
-        <v>0</v>
-      </c>
-      <c r="G5" s="2">
-        <v>0</v>
-      </c>
-      <c r="H5" s="2">
-        <v>0</v>
-      </c>
-      <c r="I5" s="2">
-        <v>0</v>
-      </c>
-      <c r="J5" s="2" t="s">
+      <c r="C20" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="F20" s="2">
+        <v>0</v>
+      </c>
+      <c r="G20" s="2">
+        <v>0</v>
+      </c>
+      <c r="H20" s="2">
+        <v>0</v>
+      </c>
+      <c r="I20" s="2">
+        <v>0</v>
+      </c>
+      <c r="J20" s="2">
+        <v>0</v>
+      </c>
+      <c r="K20" s="2" t="s">
         <v>339</v>
       </c>
-      <c r="K5" s="2" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>459</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>455</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>451</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>460</v>
-      </c>
-      <c r="E6" s="2">
-        <v>0</v>
-      </c>
-      <c r="F6" s="2">
-        <v>0</v>
-      </c>
-      <c r="G6" s="2">
-        <v>0</v>
-      </c>
-      <c r="H6" s="2">
-        <v>0</v>
-      </c>
-      <c r="I6" s="2">
-        <v>0</v>
-      </c>
-      <c r="J6" s="2" t="s">
+      <c r="L20" s="2" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="F21" s="2">
+        <v>0</v>
+      </c>
+      <c r="G21" s="2">
+        <v>0</v>
+      </c>
+      <c r="H21" s="2">
+        <v>0</v>
+      </c>
+      <c r="I21" s="2">
+        <v>0</v>
+      </c>
+      <c r="J21" s="2">
+        <v>0</v>
+      </c>
+      <c r="K21" s="2" t="s">
         <v>339</v>
       </c>
-      <c r="K6" s="2" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>461</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>452</v>
-      </c>
-      <c r="C7" s="2" t="s">
+      <c r="L21" s="2" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="F22" s="2">
+        <v>0</v>
+      </c>
+      <c r="G22" s="2">
+        <v>0</v>
+      </c>
+      <c r="H22" s="2">
+        <v>0</v>
+      </c>
+      <c r="I22" s="2">
+        <v>0</v>
+      </c>
+      <c r="J22" s="2">
+        <v>0</v>
+      </c>
+      <c r="K22" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="L22" s="2" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="F23" s="2">
+        <v>0</v>
+      </c>
+      <c r="G23" s="2">
+        <v>0</v>
+      </c>
+      <c r="H23" s="2">
+        <v>0</v>
+      </c>
+      <c r="I23" s="2">
+        <v>0</v>
+      </c>
+      <c r="J23" s="2">
+        <v>0</v>
+      </c>
+      <c r="K23" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="L23" s="2" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="D24" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E7" s="2">
-        <v>0</v>
-      </c>
-      <c r="F7" s="2">
-        <v>0</v>
-      </c>
-      <c r="G7" s="2">
-        <v>0</v>
-      </c>
-      <c r="H7" s="2">
-        <v>0</v>
-      </c>
-      <c r="I7" s="2">
-        <v>0</v>
-      </c>
-      <c r="J7" s="2" t="s">
+      <c r="E24" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="F24" s="2">
+        <v>0</v>
+      </c>
+      <c r="G24" s="2">
+        <v>0</v>
+      </c>
+      <c r="H24" s="2">
+        <v>0</v>
+      </c>
+      <c r="I24" s="2">
+        <v>0</v>
+      </c>
+      <c r="J24" s="2">
+        <v>0</v>
+      </c>
+      <c r="K24" s="2" t="s">
         <v>339</v>
       </c>
-      <c r="K7" s="2" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>463</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>455</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>461</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>464</v>
-      </c>
-      <c r="E8" s="2">
-        <v>0</v>
-      </c>
-      <c r="F8" s="2">
-        <v>0</v>
-      </c>
-      <c r="G8" s="2">
-        <v>0</v>
-      </c>
-      <c r="H8" s="2">
-        <v>0</v>
-      </c>
-      <c r="I8" s="2">
-        <v>0</v>
-      </c>
-      <c r="J8" s="2" t="s">
+      <c r="L24" s="2" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>500</v>
+      </c>
+      <c r="F25" s="2">
+        <v>0</v>
+      </c>
+      <c r="G25" s="2">
+        <v>0</v>
+      </c>
+      <c r="H25" s="2">
+        <v>0</v>
+      </c>
+      <c r="I25" s="2">
+        <v>0</v>
+      </c>
+      <c r="J25" s="2">
+        <v>0</v>
+      </c>
+      <c r="K25" s="2" t="s">
         <v>339</v>
       </c>
-      <c r="K8" s="2" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>465</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>455</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>461</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>466</v>
-      </c>
-      <c r="E9" s="2">
-        <v>0</v>
-      </c>
-      <c r="F9" s="2">
-        <v>0</v>
-      </c>
-      <c r="G9" s="2">
-        <v>0</v>
-      </c>
-      <c r="H9" s="2">
-        <v>0</v>
-      </c>
-      <c r="I9" s="2">
-        <v>0</v>
-      </c>
-      <c r="J9" s="2" t="s">
+      <c r="L25" s="2" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
+        <v>501</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="F26" s="2">
+        <v>0</v>
+      </c>
+      <c r="G26" s="2">
+        <v>0</v>
+      </c>
+      <c r="H26" s="2">
+        <v>0</v>
+      </c>
+      <c r="I26" s="2">
+        <v>0</v>
+      </c>
+      <c r="J26" s="2">
+        <v>0</v>
+      </c>
+      <c r="K26" s="2" t="s">
         <v>339</v>
       </c>
-      <c r="K9" s="2" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>467</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>455</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>461</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>468</v>
-      </c>
-      <c r="E10" s="2">
-        <v>0</v>
-      </c>
-      <c r="F10" s="2">
-        <v>0</v>
-      </c>
-      <c r="G10" s="2">
-        <v>0</v>
-      </c>
-      <c r="H10" s="2">
-        <v>0</v>
-      </c>
-      <c r="I10" s="2">
-        <v>0</v>
-      </c>
-      <c r="J10" s="2" t="s">
+      <c r="L26" s="2" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>504</v>
+      </c>
+      <c r="F27" s="2">
+        <v>0</v>
+      </c>
+      <c r="G27" s="2">
+        <v>0</v>
+      </c>
+      <c r="H27" s="2">
+        <v>0</v>
+      </c>
+      <c r="I27" s="2">
+        <v>0</v>
+      </c>
+      <c r="J27" s="2">
+        <v>0</v>
+      </c>
+      <c r="K27" s="2" t="s">
         <v>339</v>
       </c>
-      <c r="K10" s="2" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>469</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>452</v>
-      </c>
-      <c r="C11" s="2" t="s">
+      <c r="L27" s="2" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
+        <v>505</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="D28" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>470</v>
-      </c>
-      <c r="E11" s="2">
-        <v>0</v>
-      </c>
-      <c r="F11" s="2">
-        <v>0</v>
-      </c>
-      <c r="G11" s="2">
-        <v>0</v>
-      </c>
-      <c r="H11" s="2">
-        <v>0</v>
-      </c>
-      <c r="I11" s="2">
-        <v>0</v>
-      </c>
-      <c r="J11" s="2" t="s">
+      <c r="E28" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="F28" s="2">
+        <v>0</v>
+      </c>
+      <c r="G28" s="2">
+        <v>0</v>
+      </c>
+      <c r="H28" s="2">
+        <v>0</v>
+      </c>
+      <c r="I28" s="2">
+        <v>0</v>
+      </c>
+      <c r="J28" s="2">
+        <v>0</v>
+      </c>
+      <c r="K28" s="2" t="s">
         <v>339</v>
       </c>
-      <c r="K11" s="2" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
-        <v>471</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>455</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>469</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>472</v>
-      </c>
-      <c r="E12" s="2">
-        <v>0</v>
-      </c>
-      <c r="F12" s="2">
-        <v>0</v>
-      </c>
-      <c r="G12" s="2">
-        <v>0</v>
-      </c>
-      <c r="H12" s="2">
-        <v>0</v>
-      </c>
-      <c r="I12" s="2">
-        <v>0</v>
-      </c>
-      <c r="J12" s="2" t="s">
+      <c r="L28" s="2" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>505</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="F29" s="2">
+        <v>0</v>
+      </c>
+      <c r="G29" s="2">
+        <v>0</v>
+      </c>
+      <c r="H29" s="2">
+        <v>0</v>
+      </c>
+      <c r="I29" s="2">
+        <v>0</v>
+      </c>
+      <c r="J29" s="2">
+        <v>0</v>
+      </c>
+      <c r="K29" s="2" t="s">
         <v>339</v>
       </c>
-      <c r="K12" s="2" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
-        <v>473</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>455</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>469</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>474</v>
-      </c>
-      <c r="E13" s="2">
-        <v>1</v>
-      </c>
-      <c r="F13" s="2">
-        <v>1</v>
-      </c>
-      <c r="G13" s="2">
-        <v>1</v>
-      </c>
-      <c r="H13" s="2">
-        <v>1</v>
-      </c>
-      <c r="I13" s="2">
-        <v>0</v>
-      </c>
-      <c r="J13" s="2" t="s">
+      <c r="L29" s="2" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
+        <v>509</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>505</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="F30" s="2">
+        <v>0</v>
+      </c>
+      <c r="G30" s="2">
+        <v>0</v>
+      </c>
+      <c r="H30" s="2">
+        <v>0</v>
+      </c>
+      <c r="I30" s="2">
+        <v>0</v>
+      </c>
+      <c r="J30" s="2">
+        <v>0</v>
+      </c>
+      <c r="K30" s="2" t="s">
         <v>339</v>
       </c>
-      <c r="K13" s="2" t="s">
+      <c r="L30" s="2" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="C31" s="2" t="s">
         <v>450</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
-        <v>475</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>455</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>469</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>476</v>
-      </c>
-      <c r="E14" s="2">
-        <v>0</v>
-      </c>
-      <c r="F14" s="2">
-        <v>0</v>
-      </c>
-      <c r="G14" s="2">
-        <v>0</v>
-      </c>
-      <c r="H14" s="2">
-        <v>0</v>
-      </c>
-      <c r="I14" s="2">
-        <v>0</v>
-      </c>
-      <c r="J14" s="2" t="s">
+      <c r="D31" s="2" t="s">
+        <v>505</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>512</v>
+      </c>
+      <c r="F31" s="2">
+        <v>0</v>
+      </c>
+      <c r="G31" s="2">
+        <v>0</v>
+      </c>
+      <c r="H31" s="2">
+        <v>0</v>
+      </c>
+      <c r="I31" s="2">
+        <v>0</v>
+      </c>
+      <c r="J31" s="2">
+        <v>0</v>
+      </c>
+      <c r="K31" s="2" t="s">
         <v>339</v>
       </c>
-      <c r="K14" s="2" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
-        <v>477</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>452</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>478</v>
-      </c>
-      <c r="E15" s="2">
-        <v>0</v>
-      </c>
-      <c r="F15" s="2">
-        <v>0</v>
-      </c>
-      <c r="G15" s="2">
-        <v>0</v>
-      </c>
-      <c r="H15" s="2">
-        <v>0</v>
-      </c>
-      <c r="I15" s="2">
-        <v>0</v>
-      </c>
-      <c r="J15" s="2" t="s">
+      <c r="L31" s="2" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="2" t="s">
+        <v>513</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>505</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>514</v>
+      </c>
+      <c r="F32" s="2">
+        <v>0</v>
+      </c>
+      <c r="G32" s="2">
+        <v>0</v>
+      </c>
+      <c r="H32" s="2">
+        <v>0</v>
+      </c>
+      <c r="I32" s="2">
+        <v>0</v>
+      </c>
+      <c r="J32" s="2">
+        <v>0</v>
+      </c>
+      <c r="K32" s="2" t="s">
         <v>339</v>
       </c>
-      <c r="K15" s="2" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
-        <v>479</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>455</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>477</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>480</v>
-      </c>
-      <c r="E16" s="2">
-        <v>0</v>
-      </c>
-      <c r="F16" s="2">
-        <v>0</v>
-      </c>
-      <c r="G16" s="2">
-        <v>0</v>
-      </c>
-      <c r="H16" s="2">
-        <v>0</v>
-      </c>
-      <c r="I16" s="2">
-        <v>0</v>
-      </c>
-      <c r="J16" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="K16" s="2" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
-        <v>481</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>455</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>477</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>482</v>
-      </c>
-      <c r="E17" s="2">
-        <v>0</v>
-      </c>
-      <c r="F17" s="2">
-        <v>0</v>
-      </c>
-      <c r="G17" s="2">
-        <v>0</v>
-      </c>
-      <c r="H17" s="2">
-        <v>0</v>
-      </c>
-      <c r="I17" s="2">
-        <v>0</v>
-      </c>
-      <c r="J17" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="K17" s="2" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="2" t="s">
-        <v>483</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>455</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>477</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>484</v>
-      </c>
-      <c r="E18" s="2">
-        <v>0</v>
-      </c>
-      <c r="F18" s="2">
-        <v>0</v>
-      </c>
-      <c r="G18" s="2">
-        <v>0</v>
-      </c>
-      <c r="H18" s="2">
-        <v>0</v>
-      </c>
-      <c r="I18" s="2">
-        <v>0</v>
-      </c>
-      <c r="J18" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="K18" s="2" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="s">
-        <v>485</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>452</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>486</v>
-      </c>
-      <c r="E19" s="2">
-        <v>0</v>
-      </c>
-      <c r="F19" s="2">
-        <v>0</v>
-      </c>
-      <c r="G19" s="2">
-        <v>0</v>
-      </c>
-      <c r="H19" s="2">
-        <v>0</v>
-      </c>
-      <c r="I19" s="2">
-        <v>0</v>
-      </c>
-      <c r="J19" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="K19" s="2" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="2" t="s">
-        <v>487</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>455</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>485</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>488</v>
-      </c>
-      <c r="E20" s="2">
-        <v>0</v>
-      </c>
-      <c r="F20" s="2">
-        <v>0</v>
-      </c>
-      <c r="G20" s="2">
-        <v>0</v>
-      </c>
-      <c r="H20" s="2">
-        <v>0</v>
-      </c>
-      <c r="I20" s="2">
-        <v>0</v>
-      </c>
-      <c r="J20" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="K20" s="2" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="2" t="s">
-        <v>489</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>455</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>485</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>490</v>
-      </c>
-      <c r="E21" s="2">
-        <v>0</v>
-      </c>
-      <c r="F21" s="2">
-        <v>0</v>
-      </c>
-      <c r="G21" s="2">
-        <v>0</v>
-      </c>
-      <c r="H21" s="2">
-        <v>0</v>
-      </c>
-      <c r="I21" s="2">
-        <v>0</v>
-      </c>
-      <c r="J21" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="K21" s="2" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="2" t="s">
-        <v>491</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>455</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>485</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>492</v>
-      </c>
-      <c r="E22" s="2">
-        <v>0</v>
-      </c>
-      <c r="F22" s="2">
-        <v>0</v>
-      </c>
-      <c r="G22" s="2">
-        <v>0</v>
-      </c>
-      <c r="H22" s="2">
-        <v>0</v>
-      </c>
-      <c r="I22" s="2">
-        <v>0</v>
-      </c>
-      <c r="J22" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="K22" s="2" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="2" t="s">
-        <v>493</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>455</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>485</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>494</v>
-      </c>
-      <c r="E23" s="2">
-        <v>0</v>
-      </c>
-      <c r="F23" s="2">
-        <v>0</v>
-      </c>
-      <c r="G23" s="2">
-        <v>0</v>
-      </c>
-      <c r="H23" s="2">
-        <v>0</v>
-      </c>
-      <c r="I23" s="2">
-        <v>0</v>
-      </c>
-      <c r="J23" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="K23" s="2" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="2" t="s">
-        <v>495</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>452</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>496</v>
-      </c>
-      <c r="E24" s="2">
-        <v>0</v>
-      </c>
-      <c r="F24" s="2">
-        <v>0</v>
-      </c>
-      <c r="G24" s="2">
-        <v>0</v>
-      </c>
-      <c r="H24" s="2">
-        <v>0</v>
-      </c>
-      <c r="I24" s="2">
-        <v>0</v>
-      </c>
-      <c r="J24" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="K24" s="2" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="2" t="s">
-        <v>497</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>455</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>495</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>498</v>
-      </c>
-      <c r="E25" s="2">
-        <v>0</v>
-      </c>
-      <c r="F25" s="2">
-        <v>0</v>
-      </c>
-      <c r="G25" s="2">
-        <v>0</v>
-      </c>
-      <c r="H25" s="2">
-        <v>0</v>
-      </c>
-      <c r="I25" s="2">
-        <v>0</v>
-      </c>
-      <c r="J25" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="K25" s="2" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="2" t="s">
-        <v>499</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>455</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>495</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>500</v>
-      </c>
-      <c r="E26" s="2">
-        <v>0</v>
-      </c>
-      <c r="F26" s="2">
-        <v>0</v>
-      </c>
-      <c r="G26" s="2">
-        <v>0</v>
-      </c>
-      <c r="H26" s="2">
-        <v>0</v>
-      </c>
-      <c r="I26" s="2">
-        <v>0</v>
-      </c>
-      <c r="J26" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="K26" s="2" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="2" t="s">
-        <v>501</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>455</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>495</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>502</v>
-      </c>
-      <c r="E27" s="2">
-        <v>0</v>
-      </c>
-      <c r="F27" s="2">
-        <v>0</v>
-      </c>
-      <c r="G27" s="2">
-        <v>0</v>
-      </c>
-      <c r="H27" s="2">
-        <v>0</v>
-      </c>
-      <c r="I27" s="2">
-        <v>0</v>
-      </c>
-      <c r="J27" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="K27" s="2" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="2" t="s">
-        <v>503</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>452</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>504</v>
-      </c>
-      <c r="E28" s="2">
-        <v>0</v>
-      </c>
-      <c r="F28" s="2">
-        <v>0</v>
-      </c>
-      <c r="G28" s="2">
-        <v>0</v>
-      </c>
-      <c r="H28" s="2">
-        <v>0</v>
-      </c>
-      <c r="I28" s="2">
-        <v>0</v>
-      </c>
-      <c r="J28" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="K28" s="2" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="2" t="s">
-        <v>505</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>455</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>503</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>506</v>
-      </c>
-      <c r="E29" s="2">
-        <v>0</v>
-      </c>
-      <c r="F29" s="2">
-        <v>0</v>
-      </c>
-      <c r="G29" s="2">
-        <v>0</v>
-      </c>
-      <c r="H29" s="2">
-        <v>0</v>
-      </c>
-      <c r="I29" s="2">
-        <v>0</v>
-      </c>
-      <c r="J29" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="K29" s="2" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="2" t="s">
-        <v>507</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>455</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>503</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>508</v>
-      </c>
-      <c r="E30" s="2">
-        <v>0</v>
-      </c>
-      <c r="F30" s="2">
-        <v>0</v>
-      </c>
-      <c r="G30" s="2">
-        <v>0</v>
-      </c>
-      <c r="H30" s="2">
-        <v>0</v>
-      </c>
-      <c r="I30" s="2">
-        <v>0</v>
-      </c>
-      <c r="J30" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="K30" s="2" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="2" t="s">
-        <v>509</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>455</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>503</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>510</v>
-      </c>
-      <c r="E31" s="2">
-        <v>0</v>
-      </c>
-      <c r="F31" s="2">
-        <v>0</v>
-      </c>
-      <c r="G31" s="2">
-        <v>0</v>
-      </c>
-      <c r="H31" s="2">
-        <v>0</v>
-      </c>
-      <c r="I31" s="2">
-        <v>0</v>
-      </c>
-      <c r="J31" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="K31" s="2" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="2" t="s">
-        <v>511</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>455</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>503</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>512</v>
-      </c>
-      <c r="E32" s="2">
-        <v>0</v>
-      </c>
-      <c r="F32" s="2">
-        <v>0</v>
-      </c>
-      <c r="G32" s="2">
-        <v>0</v>
-      </c>
-      <c r="H32" s="2">
-        <v>0</v>
-      </c>
-      <c r="I32" s="2">
-        <v>0</v>
-      </c>
-      <c r="J32" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="K32" s="2" t="s">
+      <c r="L32" s="2" t="s">
         <v>405</v>
       </c>
     </row>
@@ -3696,19 +3798,19 @@
   <sheetData>
     <row r="1" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>50</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>314</v>
@@ -3717,19 +3819,19 @@
         <v>51</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>386</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="M1" s="1" t="s">
         <v>393</v>
@@ -3746,7 +3848,7 @@
         <v>55</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>326</v>
@@ -3761,10 +3863,10 @@
         <v>337</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="K2" s="2" t="s">
         <v>389</v>
@@ -3787,7 +3889,7 @@
         <v>55</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>340</v>
@@ -3802,10 +3904,10 @@
         <v>337</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="K3" s="2" t="s">
         <v>389</v>
@@ -3828,7 +3930,7 @@
         <v>59</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>346</v>
@@ -3843,10 +3945,10 @@
         <v>337</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>389</v>
@@ -3869,7 +3971,7 @@
         <v>63</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>354</v>
@@ -3884,10 +3986,10 @@
         <v>337</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="K5" s="2" t="s">
         <v>389</v>
@@ -3910,7 +4012,7 @@
         <v>65</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>362</v>
@@ -3925,10 +4027,10 @@
         <v>337</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="K6" s="2" t="s">
         <v>389</v>
@@ -3951,7 +4053,7 @@
         <v>67</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>370</v>
@@ -3966,10 +4068,10 @@
         <v>337</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="K7" s="2" t="s">
         <v>389</v>
@@ -3992,7 +4094,7 @@
         <v>69</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>377</v>
@@ -4007,10 +4109,10 @@
         <v>337</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="K8" s="2" t="s">
         <v>389</v>
@@ -4024,7 +4126,7 @@
     </row>
     <row r="9" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>157</v>
@@ -4033,7 +4135,7 @@
         <v>158</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>383</v>
@@ -4048,10 +4150,10 @@
         <v>337</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>389</v>
@@ -4083,36 +4185,36 @@
   <sheetData>
     <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="2" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
     </row>
   </sheetData>
@@ -4135,7 +4237,7 @@
   <sheetData>
     <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>314</v>
@@ -4144,180 +4246,180 @@
         <v>407</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
     </row>
     <row r="2" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
     </row>
     <row r="3" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
     </row>
     <row r="4" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
     </row>
     <row r="5" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
     </row>
     <row r="6" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
     </row>
     <row r="7" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
     </row>
     <row r="8" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
     </row>
     <row r="9" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
     </row>
     <row r="10" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
     </row>
     <row r="11" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
     </row>
   </sheetData>
@@ -4340,186 +4442,186 @@
   <sheetData>
     <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
     </row>
     <row r="2" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>339</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
     </row>
     <row r="3" spans="2:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B3" s="2" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>339</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
     </row>
     <row r="4" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>339</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
     </row>
     <row r="5" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>339</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
     </row>
     <row r="6" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>339</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
     </row>
     <row r="7" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>339</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
     </row>
     <row r="8" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>339</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
     </row>
     <row r="9" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
     </row>
     <row r="10" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>339</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
     </row>
     <row r="11" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>339</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
     </row>
   </sheetData>
@@ -7454,7 +7556,7 @@
         <v>389</v>
       </c>
       <c r="E2" s="2">
-        <v>1148</v>
+        <v>1054</v>
       </c>
       <c r="F2" s="2"/>
     </row>
@@ -7490,7 +7592,7 @@
         <v>389</v>
       </c>
       <c r="E4" s="2">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="F4" s="2"/>
     </row>
@@ -7508,7 +7610,7 @@
         <v>389</v>
       </c>
       <c r="E5" s="2">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="F5" s="2"/>
     </row>
@@ -7526,7 +7628,7 @@
         <v>389</v>
       </c>
       <c r="E6" s="2">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="F6" s="2"/>
     </row>
@@ -7544,7 +7646,7 @@
         <v>389</v>
       </c>
       <c r="E7" s="2">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F7" s="2"/>
     </row>
@@ -7580,7 +7682,7 @@
         <v>389</v>
       </c>
       <c r="E9" s="2">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="F9" s="2"/>
     </row>

--- a/agentic-qe-mvp/demo-artifacts/flow-1-hotel-e2e-CYC-3/09-report/CYC-3-cycle-report.xlsx
+++ b/agentic-qe-mvp/demo-artifacts/flow-1-hotel-e2e-CYC-3/09-report/CYC-3-cycle-report.xlsx
@@ -170,7 +170,7 @@
     <t>github</t>
   </si>
   <si>
-    <t>Pulled live from GitHub: git clone of sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform (452df41) at 2026-10-02T20:26:12.623Z</t>
+    <t>Pulled live from GitHub: git clone of sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform (452df41) at 2026-10-02T20:28:54.959Z</t>
   </si>
   <si>
     <t>ID</t>
@@ -1704,7 +1704,7 @@
     <t>Priya Shah</t>
   </si>
   <si>
-    <t>2026-10-02T20:26:13.414Z</t>
+    <t>2026-10-02T20:28:55.725Z</t>
   </si>
   <si>
     <t>128 requirements approved; 0 excluded; 0 conflict(s) resolved</t>
@@ -7556,7 +7556,7 @@
         <v>389</v>
       </c>
       <c r="E2" s="2">
-        <v>1054</v>
+        <v>1078</v>
       </c>
       <c r="F2" s="2"/>
     </row>
@@ -7574,7 +7574,7 @@
         <v>389</v>
       </c>
       <c r="E3" s="2">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="F3" s="2"/>
     </row>
@@ -7592,7 +7592,7 @@
         <v>389</v>
       </c>
       <c r="E4" s="2">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F4" s="2"/>
     </row>
@@ -7610,7 +7610,7 @@
         <v>389</v>
       </c>
       <c r="E5" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="F5" s="2"/>
     </row>
@@ -7628,7 +7628,7 @@
         <v>389</v>
       </c>
       <c r="E6" s="2">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="F6" s="2"/>
     </row>
@@ -7646,7 +7646,7 @@
         <v>389</v>
       </c>
       <c r="E7" s="2">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="F7" s="2"/>
     </row>
@@ -7664,7 +7664,7 @@
         <v>389</v>
       </c>
       <c r="E8" s="2">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="F8" s="2"/>
     </row>
@@ -7682,7 +7682,7 @@
         <v>389</v>
       </c>
       <c r="E9" s="2">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="F9" s="2"/>
     </row>
